--- a/News_Intelligence/output/raw_news_database_Miraee.xlsx
+++ b/News_Intelligence/output/raw_news_database_Miraee.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R563"/>
+  <dimension ref="A1:R565"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -574,12 +574,6 @@
           <t>2026-06-24 16:31:18</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -640,12 +634,6 @@
           <t>2026-06-24 16:31:18</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -706,12 +694,6 @@
           <t>2026-06-24 16:31:19</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -772,12 +754,6 @@
           <t>2026-06-24 16:31:19</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -838,12 +814,6 @@
           <t>2026-06-24 16:31:19</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -904,12 +874,6 @@
           <t>2026-06-24 16:31:18</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -970,12 +934,6 @@
           <t>2026-06-24 16:31:20</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -1036,12 +994,6 @@
           <t>2026-06-24 16:31:21</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -1102,12 +1054,6 @@
           <t>2026-06-24 16:31:24</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -1168,12 +1114,6 @@
           <t>2026-06-24 16:31:28</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -1234,12 +1174,6 @@
           <t>2026-06-24 16:31:29</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -1300,12 +1234,6 @@
           <t>2026-06-24 16:31:30</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -1366,12 +1294,6 @@
           <t>2026-06-24 16:31:29</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -1432,12 +1354,6 @@
           <t>2026-06-24 16:31:29</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -1498,12 +1414,6 @@
           <t>2026-06-24 16:31:19</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -1564,12 +1474,6 @@
           <t>2026-06-24 16:31:28</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -1630,12 +1534,6 @@
           <t>2026-06-24 16:31:28</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -1696,12 +1594,6 @@
           <t>2026-06-24 16:31:36</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -1762,12 +1654,6 @@
           <t>2026-06-24 16:31:39</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -1828,12 +1714,6 @@
           <t>2026-06-24 16:31:45</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -1894,12 +1774,6 @@
           <t>2026-06-24 16:31:47</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -1960,12 +1834,6 @@
           <t>2026-06-24 16:31:38</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -2026,12 +1894,6 @@
           <t>2026-06-24 16:31:42</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -2092,12 +1954,6 @@
           <t>2026-06-24 16:31:55</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -2158,12 +2014,6 @@
           <t>2026-06-24 16:31:39</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -2224,12 +2074,6 @@
           <t>2026-06-24 16:31:43</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -2290,12 +2134,6 @@
           <t>2026-06-24 16:31:28</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -2356,12 +2194,6 @@
           <t>2026-06-24 16:31:56</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -2422,12 +2254,6 @@
           <t>2026-06-24 16:31:52</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -2488,12 +2314,6 @@
           <t>2026-06-24 16:31:52</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -2554,12 +2374,6 @@
           <t>2026-06-24 16:32:02</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -2620,12 +2434,6 @@
           <t>2026-06-24 16:32:01</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -2686,12 +2494,6 @@
           <t>2026-06-24 16:32:03</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -2752,12 +2554,6 @@
           <t>2026-06-24 16:31:49</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -2818,12 +2614,6 @@
           <t>2026-06-24 16:32:04</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -2884,12 +2674,6 @@
           <t>2026-06-24 16:32:07</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -2950,12 +2734,6 @@
           <t>2026-06-24 16:32:06</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -3016,12 +2794,6 @@
           <t>2026-06-24 16:32:08</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -3082,12 +2854,6 @@
           <t>2026-06-24 16:32:09</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -3148,12 +2914,6 @@
           <t>2026-06-24 16:32:10</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -3214,12 +2974,6 @@
           <t>2026-06-24 16:32:07</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -3280,12 +3034,6 @@
           <t>2026-06-24 16:32:04</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -3346,12 +3094,6 @@
           <t>2026-06-24 16:32:13</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -3412,12 +3154,6 @@
           <t>2026-06-24 16:32:17</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -3478,12 +3214,6 @@
           <t>2026-06-24 16:32:15</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -3544,12 +3274,6 @@
           <t>2026-06-24 16:32:18</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -3610,12 +3334,6 @@
           <t>2026-06-24 16:32:21</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -3676,12 +3394,6 @@
           <t>2026-06-24 16:32:20</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -3742,12 +3454,6 @@
           <t>2026-06-24 16:32:23</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -3808,12 +3514,6 @@
           <t>2026-06-24 16:32:24</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -3874,12 +3574,6 @@
           <t>2026-06-24 16:32:26</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
-      <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -3940,12 +3634,6 @@
           <t>2026-06-24 16:32:11</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr"/>
-      <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr"/>
       <c r="R53" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -4006,12 +3694,6 @@
           <t>2026-06-24 16:32:26</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -4072,12 +3754,6 @@
           <t>2026-06-24 16:32:27</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr"/>
-      <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -4138,12 +3814,6 @@
           <t>2026-06-24 16:32:26</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -4204,12 +3874,6 @@
           <t>2026-06-24 16:32:27</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr"/>
-      <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -4270,12 +3934,6 @@
           <t>2026-06-24 16:32:29</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
-      <c r="O58" t="inlineStr"/>
-      <c r="P58" t="inlineStr"/>
-      <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -4336,12 +3994,6 @@
           <t>2026-06-24 16:32:30</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr"/>
-      <c r="P59" t="inlineStr"/>
-      <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -4402,12 +4054,6 @@
           <t>2026-06-24 16:32:31</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr"/>
-      <c r="P60" t="inlineStr"/>
-      <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -4468,12 +4114,6 @@
           <t>2026-06-24 16:32:33</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr"/>
-      <c r="P61" t="inlineStr"/>
-      <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -4534,12 +4174,6 @@
           <t>2026-06-24 16:32:34</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr"/>
-      <c r="P62" t="inlineStr"/>
-      <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -4600,12 +4234,6 @@
           <t>2026-06-24 16:32:34</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
-      <c r="O63" t="inlineStr"/>
-      <c r="P63" t="inlineStr"/>
-      <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -4666,12 +4294,6 @@
           <t>2026-06-24 16:32:35</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
-      <c r="O64" t="inlineStr"/>
-      <c r="P64" t="inlineStr"/>
-      <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -4732,12 +4354,6 @@
           <t>2026-06-24 16:32:35</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
-      <c r="O65" t="inlineStr"/>
-      <c r="P65" t="inlineStr"/>
-      <c r="Q65" t="inlineStr"/>
       <c r="R65" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -4798,12 +4414,6 @@
           <t>2026-06-24 16:32:38</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
-      <c r="O66" t="inlineStr"/>
-      <c r="P66" t="inlineStr"/>
-      <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -4864,12 +4474,6 @@
           <t>2026-06-24 16:32:33</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
-      <c r="O67" t="inlineStr"/>
-      <c r="P67" t="inlineStr"/>
-      <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -4930,12 +4534,6 @@
           <t>2026-06-24 16:32:39</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
-      <c r="O68" t="inlineStr"/>
-      <c r="P68" t="inlineStr"/>
-      <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -4996,12 +4594,6 @@
           <t>2026-06-24 16:32:41</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
-      <c r="O69" t="inlineStr"/>
-      <c r="P69" t="inlineStr"/>
-      <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -5062,12 +4654,6 @@
           <t>2026-06-24 16:32:43</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
-      <c r="O70" t="inlineStr"/>
-      <c r="P70" t="inlineStr"/>
-      <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -5128,12 +4714,6 @@
           <t>2026-06-24 16:32:44</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
-      <c r="O71" t="inlineStr"/>
-      <c r="P71" t="inlineStr"/>
-      <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -5194,12 +4774,6 @@
           <t>2026-06-24 16:32:44</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
-      <c r="O72" t="inlineStr"/>
-      <c r="P72" t="inlineStr"/>
-      <c r="Q72" t="inlineStr"/>
       <c r="R72" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -5260,12 +4834,6 @@
           <t>2026-06-24 16:32:46</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
-      <c r="O73" t="inlineStr"/>
-      <c r="P73" t="inlineStr"/>
-      <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -5326,12 +4894,6 @@
           <t>2026-06-24 16:32:40</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
-      <c r="O74" t="inlineStr"/>
-      <c r="P74" t="inlineStr"/>
-      <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -5392,12 +4954,6 @@
           <t>2026-06-24 16:32:40</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
-      <c r="O75" t="inlineStr"/>
-      <c r="P75" t="inlineStr"/>
-      <c r="Q75" t="inlineStr"/>
       <c r="R75" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -5458,12 +5014,6 @@
           <t>2026-06-24 16:32:50</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
-      <c r="O76" t="inlineStr"/>
-      <c r="P76" t="inlineStr"/>
-      <c r="Q76" t="inlineStr"/>
       <c r="R76" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -5524,12 +5074,6 @@
           <t>2026-06-24 16:32:49</t>
         </is>
       </c>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
-      <c r="O77" t="inlineStr"/>
-      <c r="P77" t="inlineStr"/>
-      <c r="Q77" t="inlineStr"/>
       <c r="R77" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -5590,12 +5134,6 @@
           <t>2026-06-24 16:32:47</t>
         </is>
       </c>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
-      <c r="O78" t="inlineStr"/>
-      <c r="P78" t="inlineStr"/>
-      <c r="Q78" t="inlineStr"/>
       <c r="R78" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -5656,12 +5194,6 @@
           <t>2026-06-24 16:32:51</t>
         </is>
       </c>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
-      <c r="O79" t="inlineStr"/>
-      <c r="P79" t="inlineStr"/>
-      <c r="Q79" t="inlineStr"/>
       <c r="R79" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -5722,12 +5254,6 @@
           <t>2026-06-24 16:32:54</t>
         </is>
       </c>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
-      <c r="O80" t="inlineStr"/>
-      <c r="P80" t="inlineStr"/>
-      <c r="Q80" t="inlineStr"/>
       <c r="R80" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -5788,12 +5314,6 @@
           <t>2026-06-24 16:32:55</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
-      <c r="O81" t="inlineStr"/>
-      <c r="P81" t="inlineStr"/>
-      <c r="Q81" t="inlineStr"/>
       <c r="R81" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -5854,12 +5374,6 @@
           <t>2026-06-24 16:32:56</t>
         </is>
       </c>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
-      <c r="O82" t="inlineStr"/>
-      <c r="P82" t="inlineStr"/>
-      <c r="Q82" t="inlineStr"/>
       <c r="R82" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -5920,12 +5434,6 @@
           <t>2026-06-24 16:32:57</t>
         </is>
       </c>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
-      <c r="O83" t="inlineStr"/>
-      <c r="P83" t="inlineStr"/>
-      <c r="Q83" t="inlineStr"/>
       <c r="R83" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -5986,12 +5494,6 @@
           <t>2026-06-24 16:32:57</t>
         </is>
       </c>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
-      <c r="O84" t="inlineStr"/>
-      <c r="P84" t="inlineStr"/>
-      <c r="Q84" t="inlineStr"/>
       <c r="R84" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -6052,12 +5554,6 @@
           <t>2026-06-24 16:32:58</t>
         </is>
       </c>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
-      <c r="O85" t="inlineStr"/>
-      <c r="P85" t="inlineStr"/>
-      <c r="Q85" t="inlineStr"/>
       <c r="R85" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -6118,12 +5614,6 @@
           <t>2026-06-24 16:32:59</t>
         </is>
       </c>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
-      <c r="O86" t="inlineStr"/>
-      <c r="P86" t="inlineStr"/>
-      <c r="Q86" t="inlineStr"/>
       <c r="R86" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -6184,12 +5674,6 @@
           <t>2026-06-24 16:33:00</t>
         </is>
       </c>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
-      <c r="O87" t="inlineStr"/>
-      <c r="P87" t="inlineStr"/>
-      <c r="Q87" t="inlineStr"/>
       <c r="R87" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -6250,12 +5734,6 @@
           <t>2026-06-24 16:33:00</t>
         </is>
       </c>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
-      <c r="O88" t="inlineStr"/>
-      <c r="P88" t="inlineStr"/>
-      <c r="Q88" t="inlineStr"/>
       <c r="R88" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -6316,12 +5794,6 @@
           <t>2026-06-24 16:33:07</t>
         </is>
       </c>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
-      <c r="O89" t="inlineStr"/>
-      <c r="P89" t="inlineStr"/>
-      <c r="Q89" t="inlineStr"/>
       <c r="R89" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -6382,12 +5854,6 @@
           <t>2026-06-24 16:33:07</t>
         </is>
       </c>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
-      <c r="O90" t="inlineStr"/>
-      <c r="P90" t="inlineStr"/>
-      <c r="Q90" t="inlineStr"/>
       <c r="R90" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -6448,12 +5914,6 @@
           <t>2026-06-24 16:33:07</t>
         </is>
       </c>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
-      <c r="O91" t="inlineStr"/>
-      <c r="P91" t="inlineStr"/>
-      <c r="Q91" t="inlineStr"/>
       <c r="R91" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -6514,12 +5974,6 @@
           <t>2026-06-24 16:33:08</t>
         </is>
       </c>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
-      <c r="O92" t="inlineStr"/>
-      <c r="P92" t="inlineStr"/>
-      <c r="Q92" t="inlineStr"/>
       <c r="R92" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -6580,12 +6034,6 @@
           <t>2026-06-24 16:33:09</t>
         </is>
       </c>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
-      <c r="O93" t="inlineStr"/>
-      <c r="P93" t="inlineStr"/>
-      <c r="Q93" t="inlineStr"/>
       <c r="R93" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -6646,12 +6094,6 @@
           <t>2026-06-24 16:33:07</t>
         </is>
       </c>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
-      <c r="O94" t="inlineStr"/>
-      <c r="P94" t="inlineStr"/>
-      <c r="Q94" t="inlineStr"/>
       <c r="R94" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -6712,12 +6154,6 @@
           <t>2026-06-24 16:33:07</t>
         </is>
       </c>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
-      <c r="O95" t="inlineStr"/>
-      <c r="P95" t="inlineStr"/>
-      <c r="Q95" t="inlineStr"/>
       <c r="R95" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -6778,12 +6214,6 @@
           <t>2026-06-24 16:33:08</t>
         </is>
       </c>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
-      <c r="O96" t="inlineStr"/>
-      <c r="P96" t="inlineStr"/>
-      <c r="Q96" t="inlineStr"/>
       <c r="R96" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -6844,12 +6274,6 @@
           <t>2026-06-24 16:33:09</t>
         </is>
       </c>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
-      <c r="O97" t="inlineStr"/>
-      <c r="P97" t="inlineStr"/>
-      <c r="Q97" t="inlineStr"/>
       <c r="R97" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -6910,12 +6334,6 @@
           <t>2026-06-24 16:33:10</t>
         </is>
       </c>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
-      <c r="O98" t="inlineStr"/>
-      <c r="P98" t="inlineStr"/>
-      <c r="Q98" t="inlineStr"/>
       <c r="R98" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -6976,12 +6394,6 @@
           <t>2026-06-24 16:33:15</t>
         </is>
       </c>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
-      <c r="O99" t="inlineStr"/>
-      <c r="P99" t="inlineStr"/>
-      <c r="Q99" t="inlineStr"/>
       <c r="R99" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -7042,12 +6454,6 @@
           <t>2026-06-24 16:33:16</t>
         </is>
       </c>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
-      <c r="O100" t="inlineStr"/>
-      <c r="P100" t="inlineStr"/>
-      <c r="Q100" t="inlineStr"/>
       <c r="R100" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -7108,12 +6514,6 @@
           <t>2026-06-24 16:33:17</t>
         </is>
       </c>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
-      <c r="O101" t="inlineStr"/>
-      <c r="P101" t="inlineStr"/>
-      <c r="Q101" t="inlineStr"/>
       <c r="R101" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -7174,12 +6574,6 @@
           <t>2026-06-24 16:33:19</t>
         </is>
       </c>
-      <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr"/>
-      <c r="N102" t="inlineStr"/>
-      <c r="O102" t="inlineStr"/>
-      <c r="P102" t="inlineStr"/>
-      <c r="Q102" t="inlineStr"/>
       <c r="R102" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -7240,12 +6634,6 @@
           <t>2026-06-24 16:33:20</t>
         </is>
       </c>
-      <c r="L103" t="inlineStr"/>
-      <c r="M103" t="inlineStr"/>
-      <c r="N103" t="inlineStr"/>
-      <c r="O103" t="inlineStr"/>
-      <c r="P103" t="inlineStr"/>
-      <c r="Q103" t="inlineStr"/>
       <c r="R103" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -7306,12 +6694,6 @@
           <t>2026-06-24 16:33:22</t>
         </is>
       </c>
-      <c r="L104" t="inlineStr"/>
-      <c r="M104" t="inlineStr"/>
-      <c r="N104" t="inlineStr"/>
-      <c r="O104" t="inlineStr"/>
-      <c r="P104" t="inlineStr"/>
-      <c r="Q104" t="inlineStr"/>
       <c r="R104" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -7372,12 +6754,6 @@
           <t>2026-06-24 16:33:22</t>
         </is>
       </c>
-      <c r="L105" t="inlineStr"/>
-      <c r="M105" t="inlineStr"/>
-      <c r="N105" t="inlineStr"/>
-      <c r="O105" t="inlineStr"/>
-      <c r="P105" t="inlineStr"/>
-      <c r="Q105" t="inlineStr"/>
       <c r="R105" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -7438,12 +6814,6 @@
           <t>2026-06-24 16:33:23</t>
         </is>
       </c>
-      <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr"/>
-      <c r="N106" t="inlineStr"/>
-      <c r="O106" t="inlineStr"/>
-      <c r="P106" t="inlineStr"/>
-      <c r="Q106" t="inlineStr"/>
       <c r="R106" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -7504,12 +6874,6 @@
           <t>2026-06-24 16:33:19</t>
         </is>
       </c>
-      <c r="L107" t="inlineStr"/>
-      <c r="M107" t="inlineStr"/>
-      <c r="N107" t="inlineStr"/>
-      <c r="O107" t="inlineStr"/>
-      <c r="P107" t="inlineStr"/>
-      <c r="Q107" t="inlineStr"/>
       <c r="R107" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -7570,12 +6934,6 @@
           <t>2026-06-24 16:33:30</t>
         </is>
       </c>
-      <c r="L108" t="inlineStr"/>
-      <c r="M108" t="inlineStr"/>
-      <c r="N108" t="inlineStr"/>
-      <c r="O108" t="inlineStr"/>
-      <c r="P108" t="inlineStr"/>
-      <c r="Q108" t="inlineStr"/>
       <c r="R108" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -7636,12 +6994,6 @@
           <t>2026-06-24 16:33:30</t>
         </is>
       </c>
-      <c r="L109" t="inlineStr"/>
-      <c r="M109" t="inlineStr"/>
-      <c r="N109" t="inlineStr"/>
-      <c r="O109" t="inlineStr"/>
-      <c r="P109" t="inlineStr"/>
-      <c r="Q109" t="inlineStr"/>
       <c r="R109" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -7702,12 +7054,6 @@
           <t>2026-06-24 16:33:31</t>
         </is>
       </c>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr"/>
-      <c r="N110" t="inlineStr"/>
-      <c r="O110" t="inlineStr"/>
-      <c r="P110" t="inlineStr"/>
-      <c r="Q110" t="inlineStr"/>
       <c r="R110" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -7768,12 +7114,6 @@
           <t>2026-06-24 16:33:31</t>
         </is>
       </c>
-      <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr"/>
-      <c r="N111" t="inlineStr"/>
-      <c r="O111" t="inlineStr"/>
-      <c r="P111" t="inlineStr"/>
-      <c r="Q111" t="inlineStr"/>
       <c r="R111" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -7834,12 +7174,6 @@
           <t>2026-06-24 16:33:33</t>
         </is>
       </c>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr"/>
-      <c r="N112" t="inlineStr"/>
-      <c r="O112" t="inlineStr"/>
-      <c r="P112" t="inlineStr"/>
-      <c r="Q112" t="inlineStr"/>
       <c r="R112" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -7900,12 +7234,6 @@
           <t>2026-06-24 16:33:36</t>
         </is>
       </c>
-      <c r="L113" t="inlineStr"/>
-      <c r="M113" t="inlineStr"/>
-      <c r="N113" t="inlineStr"/>
-      <c r="O113" t="inlineStr"/>
-      <c r="P113" t="inlineStr"/>
-      <c r="Q113" t="inlineStr"/>
       <c r="R113" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -7966,12 +7294,6 @@
           <t>2026-06-24 16:33:17</t>
         </is>
       </c>
-      <c r="L114" t="inlineStr"/>
-      <c r="M114" t="inlineStr"/>
-      <c r="N114" t="inlineStr"/>
-      <c r="O114" t="inlineStr"/>
-      <c r="P114" t="inlineStr"/>
-      <c r="Q114" t="inlineStr"/>
       <c r="R114" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -8032,12 +7354,6 @@
           <t>2026-06-24 16:33:26</t>
         </is>
       </c>
-      <c r="L115" t="inlineStr"/>
-      <c r="M115" t="inlineStr"/>
-      <c r="N115" t="inlineStr"/>
-      <c r="O115" t="inlineStr"/>
-      <c r="P115" t="inlineStr"/>
-      <c r="Q115" t="inlineStr"/>
       <c r="R115" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -8098,12 +7414,6 @@
           <t>2026-06-24 16:33:38</t>
         </is>
       </c>
-      <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr"/>
-      <c r="N116" t="inlineStr"/>
-      <c r="O116" t="inlineStr"/>
-      <c r="P116" t="inlineStr"/>
-      <c r="Q116" t="inlineStr"/>
       <c r="R116" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -8164,12 +7474,6 @@
           <t>2026-06-24 16:33:32</t>
         </is>
       </c>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr"/>
-      <c r="N117" t="inlineStr"/>
-      <c r="O117" t="inlineStr"/>
-      <c r="P117" t="inlineStr"/>
-      <c r="Q117" t="inlineStr"/>
       <c r="R117" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -8230,12 +7534,6 @@
           <t>2026-06-24 16:33:39</t>
         </is>
       </c>
-      <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr"/>
-      <c r="N118" t="inlineStr"/>
-      <c r="O118" t="inlineStr"/>
-      <c r="P118" t="inlineStr"/>
-      <c r="Q118" t="inlineStr"/>
       <c r="R118" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -8296,12 +7594,6 @@
           <t>2026-06-24 16:33:39</t>
         </is>
       </c>
-      <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr"/>
-      <c r="N119" t="inlineStr"/>
-      <c r="O119" t="inlineStr"/>
-      <c r="P119" t="inlineStr"/>
-      <c r="Q119" t="inlineStr"/>
       <c r="R119" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -8362,12 +7654,6 @@
           <t>2026-06-24 16:33:41</t>
         </is>
       </c>
-      <c r="L120" t="inlineStr"/>
-      <c r="M120" t="inlineStr"/>
-      <c r="N120" t="inlineStr"/>
-      <c r="O120" t="inlineStr"/>
-      <c r="P120" t="inlineStr"/>
-      <c r="Q120" t="inlineStr"/>
       <c r="R120" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -8428,12 +7714,6 @@
           <t>2026-06-24 16:33:42</t>
         </is>
       </c>
-      <c r="L121" t="inlineStr"/>
-      <c r="M121" t="inlineStr"/>
-      <c r="N121" t="inlineStr"/>
-      <c r="O121" t="inlineStr"/>
-      <c r="P121" t="inlineStr"/>
-      <c r="Q121" t="inlineStr"/>
       <c r="R121" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -8494,12 +7774,6 @@
           <t>2026-06-24 16:33:44</t>
         </is>
       </c>
-      <c r="L122" t="inlineStr"/>
-      <c r="M122" t="inlineStr"/>
-      <c r="N122" t="inlineStr"/>
-      <c r="O122" t="inlineStr"/>
-      <c r="P122" t="inlineStr"/>
-      <c r="Q122" t="inlineStr"/>
       <c r="R122" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -8560,12 +7834,6 @@
           <t>2026-06-24 16:33:44</t>
         </is>
       </c>
-      <c r="L123" t="inlineStr"/>
-      <c r="M123" t="inlineStr"/>
-      <c r="N123" t="inlineStr"/>
-      <c r="O123" t="inlineStr"/>
-      <c r="P123" t="inlineStr"/>
-      <c r="Q123" t="inlineStr"/>
       <c r="R123" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -8626,12 +7894,6 @@
           <t>2026-06-24 16:33:45</t>
         </is>
       </c>
-      <c r="L124" t="inlineStr"/>
-      <c r="M124" t="inlineStr"/>
-      <c r="N124" t="inlineStr"/>
-      <c r="O124" t="inlineStr"/>
-      <c r="P124" t="inlineStr"/>
-      <c r="Q124" t="inlineStr"/>
       <c r="R124" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -8692,12 +7954,6 @@
           <t>2026-06-24 16:33:47</t>
         </is>
       </c>
-      <c r="L125" t="inlineStr"/>
-      <c r="M125" t="inlineStr"/>
-      <c r="N125" t="inlineStr"/>
-      <c r="O125" t="inlineStr"/>
-      <c r="P125" t="inlineStr"/>
-      <c r="Q125" t="inlineStr"/>
       <c r="R125" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -8758,12 +8014,6 @@
           <t>2026-06-24 16:33:47</t>
         </is>
       </c>
-      <c r="L126" t="inlineStr"/>
-      <c r="M126" t="inlineStr"/>
-      <c r="N126" t="inlineStr"/>
-      <c r="O126" t="inlineStr"/>
-      <c r="P126" t="inlineStr"/>
-      <c r="Q126" t="inlineStr"/>
       <c r="R126" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -8824,12 +8074,6 @@
           <t>2026-06-24 16:33:47</t>
         </is>
       </c>
-      <c r="L127" t="inlineStr"/>
-      <c r="M127" t="inlineStr"/>
-      <c r="N127" t="inlineStr"/>
-      <c r="O127" t="inlineStr"/>
-      <c r="P127" t="inlineStr"/>
-      <c r="Q127" t="inlineStr"/>
       <c r="R127" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -8890,12 +8134,6 @@
           <t>2026-06-24 16:33:50</t>
         </is>
       </c>
-      <c r="L128" t="inlineStr"/>
-      <c r="M128" t="inlineStr"/>
-      <c r="N128" t="inlineStr"/>
-      <c r="O128" t="inlineStr"/>
-      <c r="P128" t="inlineStr"/>
-      <c r="Q128" t="inlineStr"/>
       <c r="R128" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -8956,12 +8194,6 @@
           <t>2026-06-24 16:33:50</t>
         </is>
       </c>
-      <c r="L129" t="inlineStr"/>
-      <c r="M129" t="inlineStr"/>
-      <c r="N129" t="inlineStr"/>
-      <c r="O129" t="inlineStr"/>
-      <c r="P129" t="inlineStr"/>
-      <c r="Q129" t="inlineStr"/>
       <c r="R129" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -9022,12 +8254,6 @@
           <t>2026-06-24 16:33:50</t>
         </is>
       </c>
-      <c r="L130" t="inlineStr"/>
-      <c r="M130" t="inlineStr"/>
-      <c r="N130" t="inlineStr"/>
-      <c r="O130" t="inlineStr"/>
-      <c r="P130" t="inlineStr"/>
-      <c r="Q130" t="inlineStr"/>
       <c r="R130" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -9088,12 +8314,6 @@
           <t>2026-06-24 16:33:52</t>
         </is>
       </c>
-      <c r="L131" t="inlineStr"/>
-      <c r="M131" t="inlineStr"/>
-      <c r="N131" t="inlineStr"/>
-      <c r="O131" t="inlineStr"/>
-      <c r="P131" t="inlineStr"/>
-      <c r="Q131" t="inlineStr"/>
       <c r="R131" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -9154,12 +8374,6 @@
           <t>2026-06-24 16:33:52</t>
         </is>
       </c>
-      <c r="L132" t="inlineStr"/>
-      <c r="M132" t="inlineStr"/>
-      <c r="N132" t="inlineStr"/>
-      <c r="O132" t="inlineStr"/>
-      <c r="P132" t="inlineStr"/>
-      <c r="Q132" t="inlineStr"/>
       <c r="R132" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -9220,12 +8434,6 @@
           <t>2026-06-24 16:33:54</t>
         </is>
       </c>
-      <c r="L133" t="inlineStr"/>
-      <c r="M133" t="inlineStr"/>
-      <c r="N133" t="inlineStr"/>
-      <c r="O133" t="inlineStr"/>
-      <c r="P133" t="inlineStr"/>
-      <c r="Q133" t="inlineStr"/>
       <c r="R133" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -9286,12 +8494,6 @@
           <t>2026-06-24 16:33:54</t>
         </is>
       </c>
-      <c r="L134" t="inlineStr"/>
-      <c r="M134" t="inlineStr"/>
-      <c r="N134" t="inlineStr"/>
-      <c r="O134" t="inlineStr"/>
-      <c r="P134" t="inlineStr"/>
-      <c r="Q134" t="inlineStr"/>
       <c r="R134" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -9352,12 +8554,6 @@
           <t>2026-06-24 16:33:54</t>
         </is>
       </c>
-      <c r="L135" t="inlineStr"/>
-      <c r="M135" t="inlineStr"/>
-      <c r="N135" t="inlineStr"/>
-      <c r="O135" t="inlineStr"/>
-      <c r="P135" t="inlineStr"/>
-      <c r="Q135" t="inlineStr"/>
       <c r="R135" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -9418,12 +8614,6 @@
           <t>2026-06-24 16:33:59</t>
         </is>
       </c>
-      <c r="L136" t="inlineStr"/>
-      <c r="M136" t="inlineStr"/>
-      <c r="N136" t="inlineStr"/>
-      <c r="O136" t="inlineStr"/>
-      <c r="P136" t="inlineStr"/>
-      <c r="Q136" t="inlineStr"/>
       <c r="R136" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -9484,12 +8674,6 @@
           <t>2026-06-24 16:34:01</t>
         </is>
       </c>
-      <c r="L137" t="inlineStr"/>
-      <c r="M137" t="inlineStr"/>
-      <c r="N137" t="inlineStr"/>
-      <c r="O137" t="inlineStr"/>
-      <c r="P137" t="inlineStr"/>
-      <c r="Q137" t="inlineStr"/>
       <c r="R137" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -9551,12 +8735,6 @@
           <t>2026-06-24 16:34:01</t>
         </is>
       </c>
-      <c r="L138" t="inlineStr"/>
-      <c r="M138" t="inlineStr"/>
-      <c r="N138" t="inlineStr"/>
-      <c r="O138" t="inlineStr"/>
-      <c r="P138" t="inlineStr"/>
-      <c r="Q138" t="inlineStr"/>
       <c r="R138" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -9620,12 +8798,6 @@
           <t>2026-06-24 16:34:02</t>
         </is>
       </c>
-      <c r="L139" t="inlineStr"/>
-      <c r="M139" t="inlineStr"/>
-      <c r="N139" t="inlineStr"/>
-      <c r="O139" t="inlineStr"/>
-      <c r="P139" t="inlineStr"/>
-      <c r="Q139" t="inlineStr"/>
       <c r="R139" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -9686,12 +8858,6 @@
           <t>2026-06-24 16:34:04</t>
         </is>
       </c>
-      <c r="L140" t="inlineStr"/>
-      <c r="M140" t="inlineStr"/>
-      <c r="N140" t="inlineStr"/>
-      <c r="O140" t="inlineStr"/>
-      <c r="P140" t="inlineStr"/>
-      <c r="Q140" t="inlineStr"/>
       <c r="R140" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -9752,12 +8918,6 @@
           <t>2026-06-24 16:34:05</t>
         </is>
       </c>
-      <c r="L141" t="inlineStr"/>
-      <c r="M141" t="inlineStr"/>
-      <c r="N141" t="inlineStr"/>
-      <c r="O141" t="inlineStr"/>
-      <c r="P141" t="inlineStr"/>
-      <c r="Q141" t="inlineStr"/>
       <c r="R141" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -9818,12 +8978,6 @@
           <t>2026-06-24 16:34:06</t>
         </is>
       </c>
-      <c r="L142" t="inlineStr"/>
-      <c r="M142" t="inlineStr"/>
-      <c r="N142" t="inlineStr"/>
-      <c r="O142" t="inlineStr"/>
-      <c r="P142" t="inlineStr"/>
-      <c r="Q142" t="inlineStr"/>
       <c r="R142" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -9884,12 +9038,6 @@
           <t>2026-06-24 16:34:01</t>
         </is>
       </c>
-      <c r="L143" t="inlineStr"/>
-      <c r="M143" t="inlineStr"/>
-      <c r="N143" t="inlineStr"/>
-      <c r="O143" t="inlineStr"/>
-      <c r="P143" t="inlineStr"/>
-      <c r="Q143" t="inlineStr"/>
       <c r="R143" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -9950,12 +9098,6 @@
           <t>2026-06-24 16:34:09</t>
         </is>
       </c>
-      <c r="L144" t="inlineStr"/>
-      <c r="M144" t="inlineStr"/>
-      <c r="N144" t="inlineStr"/>
-      <c r="O144" t="inlineStr"/>
-      <c r="P144" t="inlineStr"/>
-      <c r="Q144" t="inlineStr"/>
       <c r="R144" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -10016,12 +9158,6 @@
           <t>2026-06-24 16:34:05</t>
         </is>
       </c>
-      <c r="L145" t="inlineStr"/>
-      <c r="M145" t="inlineStr"/>
-      <c r="N145" t="inlineStr"/>
-      <c r="O145" t="inlineStr"/>
-      <c r="P145" t="inlineStr"/>
-      <c r="Q145" t="inlineStr"/>
       <c r="R145" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -10082,12 +9218,6 @@
           <t>2026-06-24 16:34:03</t>
         </is>
       </c>
-      <c r="L146" t="inlineStr"/>
-      <c r="M146" t="inlineStr"/>
-      <c r="N146" t="inlineStr"/>
-      <c r="O146" t="inlineStr"/>
-      <c r="P146" t="inlineStr"/>
-      <c r="Q146" t="inlineStr"/>
       <c r="R146" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -10148,12 +9278,6 @@
           <t>2026-06-24 16:34:12</t>
         </is>
       </c>
-      <c r="L147" t="inlineStr"/>
-      <c r="M147" t="inlineStr"/>
-      <c r="N147" t="inlineStr"/>
-      <c r="O147" t="inlineStr"/>
-      <c r="P147" t="inlineStr"/>
-      <c r="Q147" t="inlineStr"/>
       <c r="R147" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -10214,12 +9338,6 @@
           <t>2026-06-24 16:34:12</t>
         </is>
       </c>
-      <c r="L148" t="inlineStr"/>
-      <c r="M148" t="inlineStr"/>
-      <c r="N148" t="inlineStr"/>
-      <c r="O148" t="inlineStr"/>
-      <c r="P148" t="inlineStr"/>
-      <c r="Q148" t="inlineStr"/>
       <c r="R148" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -10281,12 +9399,6 @@
           <t>2026-06-24 16:34:15</t>
         </is>
       </c>
-      <c r="L149" t="inlineStr"/>
-      <c r="M149" t="inlineStr"/>
-      <c r="N149" t="inlineStr"/>
-      <c r="O149" t="inlineStr"/>
-      <c r="P149" t="inlineStr"/>
-      <c r="Q149" t="inlineStr"/>
       <c r="R149" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -10347,12 +9459,6 @@
           <t>2026-06-24 16:34:17</t>
         </is>
       </c>
-      <c r="L150" t="inlineStr"/>
-      <c r="M150" t="inlineStr"/>
-      <c r="N150" t="inlineStr"/>
-      <c r="O150" t="inlineStr"/>
-      <c r="P150" t="inlineStr"/>
-      <c r="Q150" t="inlineStr"/>
       <c r="R150" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -10413,12 +9519,6 @@
           <t>2026-06-24 16:34:15</t>
         </is>
       </c>
-      <c r="L151" t="inlineStr"/>
-      <c r="M151" t="inlineStr"/>
-      <c r="N151" t="inlineStr"/>
-      <c r="O151" t="inlineStr"/>
-      <c r="P151" t="inlineStr"/>
-      <c r="Q151" t="inlineStr"/>
       <c r="R151" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -10479,12 +9579,6 @@
           <t>2026-06-24 16:34:17</t>
         </is>
       </c>
-      <c r="L152" t="inlineStr"/>
-      <c r="M152" t="inlineStr"/>
-      <c r="N152" t="inlineStr"/>
-      <c r="O152" t="inlineStr"/>
-      <c r="P152" t="inlineStr"/>
-      <c r="Q152" t="inlineStr"/>
       <c r="R152" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -10545,12 +9639,6 @@
           <t>2026-06-24 16:34:17</t>
         </is>
       </c>
-      <c r="L153" t="inlineStr"/>
-      <c r="M153" t="inlineStr"/>
-      <c r="N153" t="inlineStr"/>
-      <c r="O153" t="inlineStr"/>
-      <c r="P153" t="inlineStr"/>
-      <c r="Q153" t="inlineStr"/>
       <c r="R153" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -10611,12 +9699,6 @@
           <t>2026-06-24 16:34:19</t>
         </is>
       </c>
-      <c r="L154" t="inlineStr"/>
-      <c r="M154" t="inlineStr"/>
-      <c r="N154" t="inlineStr"/>
-      <c r="O154" t="inlineStr"/>
-      <c r="P154" t="inlineStr"/>
-      <c r="Q154" t="inlineStr"/>
       <c r="R154" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -10677,12 +9759,6 @@
           <t>2026-06-24 16:34:10</t>
         </is>
       </c>
-      <c r="L155" t="inlineStr"/>
-      <c r="M155" t="inlineStr"/>
-      <c r="N155" t="inlineStr"/>
-      <c r="O155" t="inlineStr"/>
-      <c r="P155" t="inlineStr"/>
-      <c r="Q155" t="inlineStr"/>
       <c r="R155" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -10743,12 +9819,6 @@
           <t>2026-06-24 16:34:20</t>
         </is>
       </c>
-      <c r="L156" t="inlineStr"/>
-      <c r="M156" t="inlineStr"/>
-      <c r="N156" t="inlineStr"/>
-      <c r="O156" t="inlineStr"/>
-      <c r="P156" t="inlineStr"/>
-      <c r="Q156" t="inlineStr"/>
       <c r="R156" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -10809,12 +9879,6 @@
           <t>2026-06-24 16:34:17</t>
         </is>
       </c>
-      <c r="L157" t="inlineStr"/>
-      <c r="M157" t="inlineStr"/>
-      <c r="N157" t="inlineStr"/>
-      <c r="O157" t="inlineStr"/>
-      <c r="P157" t="inlineStr"/>
-      <c r="Q157" t="inlineStr"/>
       <c r="R157" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -10876,12 +9940,6 @@
           <t>2026-06-24 16:34:25</t>
         </is>
       </c>
-      <c r="L158" t="inlineStr"/>
-      <c r="M158" t="inlineStr"/>
-      <c r="N158" t="inlineStr"/>
-      <c r="O158" t="inlineStr"/>
-      <c r="P158" t="inlineStr"/>
-      <c r="Q158" t="inlineStr"/>
       <c r="R158" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -10942,12 +10000,6 @@
           <t>2026-06-24 16:34:25</t>
         </is>
       </c>
-      <c r="L159" t="inlineStr"/>
-      <c r="M159" t="inlineStr"/>
-      <c r="N159" t="inlineStr"/>
-      <c r="O159" t="inlineStr"/>
-      <c r="P159" t="inlineStr"/>
-      <c r="Q159" t="inlineStr"/>
       <c r="R159" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -11008,12 +10060,6 @@
           <t>2026-06-24 16:34:25</t>
         </is>
       </c>
-      <c r="L160" t="inlineStr"/>
-      <c r="M160" t="inlineStr"/>
-      <c r="N160" t="inlineStr"/>
-      <c r="O160" t="inlineStr"/>
-      <c r="P160" t="inlineStr"/>
-      <c r="Q160" t="inlineStr"/>
       <c r="R160" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -11074,12 +10120,6 @@
           <t>2026-06-24 16:34:25</t>
         </is>
       </c>
-      <c r="L161" t="inlineStr"/>
-      <c r="M161" t="inlineStr"/>
-      <c r="N161" t="inlineStr"/>
-      <c r="O161" t="inlineStr"/>
-      <c r="P161" t="inlineStr"/>
-      <c r="Q161" t="inlineStr"/>
       <c r="R161" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -11140,12 +10180,6 @@
           <t>2026-06-24 16:34:27</t>
         </is>
       </c>
-      <c r="L162" t="inlineStr"/>
-      <c r="M162" t="inlineStr"/>
-      <c r="N162" t="inlineStr"/>
-      <c r="O162" t="inlineStr"/>
-      <c r="P162" t="inlineStr"/>
-      <c r="Q162" t="inlineStr"/>
       <c r="R162" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -11206,12 +10240,6 @@
           <t>2026-06-24 16:34:29</t>
         </is>
       </c>
-      <c r="L163" t="inlineStr"/>
-      <c r="M163" t="inlineStr"/>
-      <c r="N163" t="inlineStr"/>
-      <c r="O163" t="inlineStr"/>
-      <c r="P163" t="inlineStr"/>
-      <c r="Q163" t="inlineStr"/>
       <c r="R163" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -11272,12 +10300,6 @@
           <t>2026-06-24 16:34:33</t>
         </is>
       </c>
-      <c r="L164" t="inlineStr"/>
-      <c r="M164" t="inlineStr"/>
-      <c r="N164" t="inlineStr"/>
-      <c r="O164" t="inlineStr"/>
-      <c r="P164" t="inlineStr"/>
-      <c r="Q164" t="inlineStr"/>
       <c r="R164" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -11338,12 +10360,6 @@
           <t>2026-06-24 16:34:34</t>
         </is>
       </c>
-      <c r="L165" t="inlineStr"/>
-      <c r="M165" t="inlineStr"/>
-      <c r="N165" t="inlineStr"/>
-      <c r="O165" t="inlineStr"/>
-      <c r="P165" t="inlineStr"/>
-      <c r="Q165" t="inlineStr"/>
       <c r="R165" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -11404,12 +10420,6 @@
           <t>2026-06-24 16:34:37</t>
         </is>
       </c>
-      <c r="L166" t="inlineStr"/>
-      <c r="M166" t="inlineStr"/>
-      <c r="N166" t="inlineStr"/>
-      <c r="O166" t="inlineStr"/>
-      <c r="P166" t="inlineStr"/>
-      <c r="Q166" t="inlineStr"/>
       <c r="R166" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -11470,12 +10480,6 @@
           <t>2026-06-24 16:34:39</t>
         </is>
       </c>
-      <c r="L167" t="inlineStr"/>
-      <c r="M167" t="inlineStr"/>
-      <c r="N167" t="inlineStr"/>
-      <c r="O167" t="inlineStr"/>
-      <c r="P167" t="inlineStr"/>
-      <c r="Q167" t="inlineStr"/>
       <c r="R167" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -11536,12 +10540,6 @@
           <t>2026-06-24 16:34:38</t>
         </is>
       </c>
-      <c r="L168" t="inlineStr"/>
-      <c r="M168" t="inlineStr"/>
-      <c r="N168" t="inlineStr"/>
-      <c r="O168" t="inlineStr"/>
-      <c r="P168" t="inlineStr"/>
-      <c r="Q168" t="inlineStr"/>
       <c r="R168" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -11602,12 +10600,6 @@
           <t>2026-06-24 16:34:38</t>
         </is>
       </c>
-      <c r="L169" t="inlineStr"/>
-      <c r="M169" t="inlineStr"/>
-      <c r="N169" t="inlineStr"/>
-      <c r="O169" t="inlineStr"/>
-      <c r="P169" t="inlineStr"/>
-      <c r="Q169" t="inlineStr"/>
       <c r="R169" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -11668,12 +10660,6 @@
           <t>2026-06-24 16:34:27</t>
         </is>
       </c>
-      <c r="L170" t="inlineStr"/>
-      <c r="M170" t="inlineStr"/>
-      <c r="N170" t="inlineStr"/>
-      <c r="O170" t="inlineStr"/>
-      <c r="P170" t="inlineStr"/>
-      <c r="Q170" t="inlineStr"/>
       <c r="R170" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -11734,12 +10720,6 @@
           <t>2026-06-24 16:34:32</t>
         </is>
       </c>
-      <c r="L171" t="inlineStr"/>
-      <c r="M171" t="inlineStr"/>
-      <c r="N171" t="inlineStr"/>
-      <c r="O171" t="inlineStr"/>
-      <c r="P171" t="inlineStr"/>
-      <c r="Q171" t="inlineStr"/>
       <c r="R171" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -11800,12 +10780,6 @@
           <t>2026-06-24 16:34:45</t>
         </is>
       </c>
-      <c r="L172" t="inlineStr"/>
-      <c r="M172" t="inlineStr"/>
-      <c r="N172" t="inlineStr"/>
-      <c r="O172" t="inlineStr"/>
-      <c r="P172" t="inlineStr"/>
-      <c r="Q172" t="inlineStr"/>
       <c r="R172" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -11866,12 +10840,6 @@
           <t>2026-06-24 16:34:48</t>
         </is>
       </c>
-      <c r="L173" t="inlineStr"/>
-      <c r="M173" t="inlineStr"/>
-      <c r="N173" t="inlineStr"/>
-      <c r="O173" t="inlineStr"/>
-      <c r="P173" t="inlineStr"/>
-      <c r="Q173" t="inlineStr"/>
       <c r="R173" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -11932,12 +10900,6 @@
           <t>2026-06-24 16:34:47</t>
         </is>
       </c>
-      <c r="L174" t="inlineStr"/>
-      <c r="M174" t="inlineStr"/>
-      <c r="N174" t="inlineStr"/>
-      <c r="O174" t="inlineStr"/>
-      <c r="P174" t="inlineStr"/>
-      <c r="Q174" t="inlineStr"/>
       <c r="R174" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -11998,12 +10960,6 @@
           <t>2026-06-24 16:34:48</t>
         </is>
       </c>
-      <c r="L175" t="inlineStr"/>
-      <c r="M175" t="inlineStr"/>
-      <c r="N175" t="inlineStr"/>
-      <c r="O175" t="inlineStr"/>
-      <c r="P175" t="inlineStr"/>
-      <c r="Q175" t="inlineStr"/>
       <c r="R175" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -12064,12 +11020,6 @@
           <t>2026-06-24 16:34:49</t>
         </is>
       </c>
-      <c r="L176" t="inlineStr"/>
-      <c r="M176" t="inlineStr"/>
-      <c r="N176" t="inlineStr"/>
-      <c r="O176" t="inlineStr"/>
-      <c r="P176" t="inlineStr"/>
-      <c r="Q176" t="inlineStr"/>
       <c r="R176" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -12130,12 +11080,6 @@
           <t>2026-06-24 16:34:50</t>
         </is>
       </c>
-      <c r="L177" t="inlineStr"/>
-      <c r="M177" t="inlineStr"/>
-      <c r="N177" t="inlineStr"/>
-      <c r="O177" t="inlineStr"/>
-      <c r="P177" t="inlineStr"/>
-      <c r="Q177" t="inlineStr"/>
       <c r="R177" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -12196,12 +11140,6 @@
           <t>2026-06-24 16:34:38</t>
         </is>
       </c>
-      <c r="L178" t="inlineStr"/>
-      <c r="M178" t="inlineStr"/>
-      <c r="N178" t="inlineStr"/>
-      <c r="O178" t="inlineStr"/>
-      <c r="P178" t="inlineStr"/>
-      <c r="Q178" t="inlineStr"/>
       <c r="R178" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -12262,12 +11200,6 @@
           <t>2026-06-24 16:34:55</t>
         </is>
       </c>
-      <c r="L179" t="inlineStr"/>
-      <c r="M179" t="inlineStr"/>
-      <c r="N179" t="inlineStr"/>
-      <c r="O179" t="inlineStr"/>
-      <c r="P179" t="inlineStr"/>
-      <c r="Q179" t="inlineStr"/>
       <c r="R179" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -12328,12 +11260,6 @@
           <t>2026-06-24 16:34:42</t>
         </is>
       </c>
-      <c r="L180" t="inlineStr"/>
-      <c r="M180" t="inlineStr"/>
-      <c r="N180" t="inlineStr"/>
-      <c r="O180" t="inlineStr"/>
-      <c r="P180" t="inlineStr"/>
-      <c r="Q180" t="inlineStr"/>
       <c r="R180" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -12394,12 +11320,6 @@
           <t>2026-06-24 16:34:53</t>
         </is>
       </c>
-      <c r="L181" t="inlineStr"/>
-      <c r="M181" t="inlineStr"/>
-      <c r="N181" t="inlineStr"/>
-      <c r="O181" t="inlineStr"/>
-      <c r="P181" t="inlineStr"/>
-      <c r="Q181" t="inlineStr"/>
       <c r="R181" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -12460,12 +11380,6 @@
           <t>2026-06-24 16:34:58</t>
         </is>
       </c>
-      <c r="L182" t="inlineStr"/>
-      <c r="M182" t="inlineStr"/>
-      <c r="N182" t="inlineStr"/>
-      <c r="O182" t="inlineStr"/>
-      <c r="P182" t="inlineStr"/>
-      <c r="Q182" t="inlineStr"/>
       <c r="R182" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -12526,12 +11440,6 @@
           <t>2026-06-24 16:34:58</t>
         </is>
       </c>
-      <c r="L183" t="inlineStr"/>
-      <c r="M183" t="inlineStr"/>
-      <c r="N183" t="inlineStr"/>
-      <c r="O183" t="inlineStr"/>
-      <c r="P183" t="inlineStr"/>
-      <c r="Q183" t="inlineStr"/>
       <c r="R183" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -12592,12 +11500,6 @@
           <t>2026-06-24 16:34:58</t>
         </is>
       </c>
-      <c r="L184" t="inlineStr"/>
-      <c r="M184" t="inlineStr"/>
-      <c r="N184" t="inlineStr"/>
-      <c r="O184" t="inlineStr"/>
-      <c r="P184" t="inlineStr"/>
-      <c r="Q184" t="inlineStr"/>
       <c r="R184" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -12658,12 +11560,6 @@
           <t>2026-06-24 16:34:57</t>
         </is>
       </c>
-      <c r="L185" t="inlineStr"/>
-      <c r="M185" t="inlineStr"/>
-      <c r="N185" t="inlineStr"/>
-      <c r="O185" t="inlineStr"/>
-      <c r="P185" t="inlineStr"/>
-      <c r="Q185" t="inlineStr"/>
       <c r="R185" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -12725,12 +11621,6 @@
           <t>2026-06-24 16:35:00</t>
         </is>
       </c>
-      <c r="L186" t="inlineStr"/>
-      <c r="M186" t="inlineStr"/>
-      <c r="N186" t="inlineStr"/>
-      <c r="O186" t="inlineStr"/>
-      <c r="P186" t="inlineStr"/>
-      <c r="Q186" t="inlineStr"/>
       <c r="R186" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -12791,12 +11681,6 @@
           <t>2026-06-24 16:34:43</t>
         </is>
       </c>
-      <c r="L187" t="inlineStr"/>
-      <c r="M187" t="inlineStr"/>
-      <c r="N187" t="inlineStr"/>
-      <c r="O187" t="inlineStr"/>
-      <c r="P187" t="inlineStr"/>
-      <c r="Q187" t="inlineStr"/>
       <c r="R187" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -12857,12 +11741,6 @@
           <t>2026-06-24 16:35:00</t>
         </is>
       </c>
-      <c r="L188" t="inlineStr"/>
-      <c r="M188" t="inlineStr"/>
-      <c r="N188" t="inlineStr"/>
-      <c r="O188" t="inlineStr"/>
-      <c r="P188" t="inlineStr"/>
-      <c r="Q188" t="inlineStr"/>
       <c r="R188" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -12923,12 +11801,6 @@
           <t>2026-06-24 16:35:03</t>
         </is>
       </c>
-      <c r="L189" t="inlineStr"/>
-      <c r="M189" t="inlineStr"/>
-      <c r="N189" t="inlineStr"/>
-      <c r="O189" t="inlineStr"/>
-      <c r="P189" t="inlineStr"/>
-      <c r="Q189" t="inlineStr"/>
       <c r="R189" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -12989,12 +11861,6 @@
           <t>2026-06-24 16:35:04</t>
         </is>
       </c>
-      <c r="L190" t="inlineStr"/>
-      <c r="M190" t="inlineStr"/>
-      <c r="N190" t="inlineStr"/>
-      <c r="O190" t="inlineStr"/>
-      <c r="P190" t="inlineStr"/>
-      <c r="Q190" t="inlineStr"/>
       <c r="R190" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -13055,12 +11921,6 @@
           <t>2026-06-24 16:35:04</t>
         </is>
       </c>
-      <c r="L191" t="inlineStr"/>
-      <c r="M191" t="inlineStr"/>
-      <c r="N191" t="inlineStr"/>
-      <c r="O191" t="inlineStr"/>
-      <c r="P191" t="inlineStr"/>
-      <c r="Q191" t="inlineStr"/>
       <c r="R191" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -13121,12 +11981,6 @@
           <t>2026-06-24 16:35:05</t>
         </is>
       </c>
-      <c r="L192" t="inlineStr"/>
-      <c r="M192" t="inlineStr"/>
-      <c r="N192" t="inlineStr"/>
-      <c r="O192" t="inlineStr"/>
-      <c r="P192" t="inlineStr"/>
-      <c r="Q192" t="inlineStr"/>
       <c r="R192" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -13187,12 +12041,6 @@
           <t>2026-06-24 16:35:04</t>
         </is>
       </c>
-      <c r="L193" t="inlineStr"/>
-      <c r="M193" t="inlineStr"/>
-      <c r="N193" t="inlineStr"/>
-      <c r="O193" t="inlineStr"/>
-      <c r="P193" t="inlineStr"/>
-      <c r="Q193" t="inlineStr"/>
       <c r="R193" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -13253,12 +12101,6 @@
           <t>2026-06-24 16:35:06</t>
         </is>
       </c>
-      <c r="L194" t="inlineStr"/>
-      <c r="M194" t="inlineStr"/>
-      <c r="N194" t="inlineStr"/>
-      <c r="O194" t="inlineStr"/>
-      <c r="P194" t="inlineStr"/>
-      <c r="Q194" t="inlineStr"/>
       <c r="R194" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -13319,12 +12161,6 @@
           <t>2026-06-24 16:35:06</t>
         </is>
       </c>
-      <c r="L195" t="inlineStr"/>
-      <c r="M195" t="inlineStr"/>
-      <c r="N195" t="inlineStr"/>
-      <c r="O195" t="inlineStr"/>
-      <c r="P195" t="inlineStr"/>
-      <c r="Q195" t="inlineStr"/>
       <c r="R195" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -13385,12 +12221,6 @@
           <t>2026-06-24 16:35:07</t>
         </is>
       </c>
-      <c r="L196" t="inlineStr"/>
-      <c r="M196" t="inlineStr"/>
-      <c r="N196" t="inlineStr"/>
-      <c r="O196" t="inlineStr"/>
-      <c r="P196" t="inlineStr"/>
-      <c r="Q196" t="inlineStr"/>
       <c r="R196" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -13451,12 +12281,6 @@
           <t>2026-06-24 16:35:11</t>
         </is>
       </c>
-      <c r="L197" t="inlineStr"/>
-      <c r="M197" t="inlineStr"/>
-      <c r="N197" t="inlineStr"/>
-      <c r="O197" t="inlineStr"/>
-      <c r="P197" t="inlineStr"/>
-      <c r="Q197" t="inlineStr"/>
       <c r="R197" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -13517,12 +12341,6 @@
           <t>2026-06-24 16:35:12</t>
         </is>
       </c>
-      <c r="L198" t="inlineStr"/>
-      <c r="M198" t="inlineStr"/>
-      <c r="N198" t="inlineStr"/>
-      <c r="O198" t="inlineStr"/>
-      <c r="P198" t="inlineStr"/>
-      <c r="Q198" t="inlineStr"/>
       <c r="R198" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -13583,12 +12401,6 @@
           <t>2026-06-24 16:35:10</t>
         </is>
       </c>
-      <c r="L199" t="inlineStr"/>
-      <c r="M199" t="inlineStr"/>
-      <c r="N199" t="inlineStr"/>
-      <c r="O199" t="inlineStr"/>
-      <c r="P199" t="inlineStr"/>
-      <c r="Q199" t="inlineStr"/>
       <c r="R199" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -13649,12 +12461,6 @@
           <t>2026-06-24 16:35:13</t>
         </is>
       </c>
-      <c r="L200" t="inlineStr"/>
-      <c r="M200" t="inlineStr"/>
-      <c r="N200" t="inlineStr"/>
-      <c r="O200" t="inlineStr"/>
-      <c r="P200" t="inlineStr"/>
-      <c r="Q200" t="inlineStr"/>
       <c r="R200" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -13715,12 +12521,6 @@
           <t>2026-06-24 16:35:14</t>
         </is>
       </c>
-      <c r="L201" t="inlineStr"/>
-      <c r="M201" t="inlineStr"/>
-      <c r="N201" t="inlineStr"/>
-      <c r="O201" t="inlineStr"/>
-      <c r="P201" t="inlineStr"/>
-      <c r="Q201" t="inlineStr"/>
       <c r="R201" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -13781,12 +12581,6 @@
           <t>2026-06-24 16:35:13</t>
         </is>
       </c>
-      <c r="L202" t="inlineStr"/>
-      <c r="M202" t="inlineStr"/>
-      <c r="N202" t="inlineStr"/>
-      <c r="O202" t="inlineStr"/>
-      <c r="P202" t="inlineStr"/>
-      <c r="Q202" t="inlineStr"/>
       <c r="R202" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -13847,12 +12641,6 @@
           <t>2026-06-24 16:35:16</t>
         </is>
       </c>
-      <c r="L203" t="inlineStr"/>
-      <c r="M203" t="inlineStr"/>
-      <c r="N203" t="inlineStr"/>
-      <c r="O203" t="inlineStr"/>
-      <c r="P203" t="inlineStr"/>
-      <c r="Q203" t="inlineStr"/>
       <c r="R203" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -13913,12 +12701,6 @@
           <t>2026-06-24 16:35:07</t>
         </is>
       </c>
-      <c r="L204" t="inlineStr"/>
-      <c r="M204" t="inlineStr"/>
-      <c r="N204" t="inlineStr"/>
-      <c r="O204" t="inlineStr"/>
-      <c r="P204" t="inlineStr"/>
-      <c r="Q204" t="inlineStr"/>
       <c r="R204" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -13979,12 +12761,6 @@
           <t>2026-06-24 16:35:17</t>
         </is>
       </c>
-      <c r="L205" t="inlineStr"/>
-      <c r="M205" t="inlineStr"/>
-      <c r="N205" t="inlineStr"/>
-      <c r="O205" t="inlineStr"/>
-      <c r="P205" t="inlineStr"/>
-      <c r="Q205" t="inlineStr"/>
       <c r="R205" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -14045,12 +12821,6 @@
           <t>2026-06-24 16:35:18</t>
         </is>
       </c>
-      <c r="L206" t="inlineStr"/>
-      <c r="M206" t="inlineStr"/>
-      <c r="N206" t="inlineStr"/>
-      <c r="O206" t="inlineStr"/>
-      <c r="P206" t="inlineStr"/>
-      <c r="Q206" t="inlineStr"/>
       <c r="R206" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -14111,12 +12881,6 @@
           <t>2026-06-24 16:35:19</t>
         </is>
       </c>
-      <c r="L207" t="inlineStr"/>
-      <c r="M207" t="inlineStr"/>
-      <c r="N207" t="inlineStr"/>
-      <c r="O207" t="inlineStr"/>
-      <c r="P207" t="inlineStr"/>
-      <c r="Q207" t="inlineStr"/>
       <c r="R207" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -14177,12 +12941,6 @@
           <t>2026-06-24 16:35:20</t>
         </is>
       </c>
-      <c r="L208" t="inlineStr"/>
-      <c r="M208" t="inlineStr"/>
-      <c r="N208" t="inlineStr"/>
-      <c r="O208" t="inlineStr"/>
-      <c r="P208" t="inlineStr"/>
-      <c r="Q208" t="inlineStr"/>
       <c r="R208" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -14243,12 +13001,6 @@
           <t>2026-06-24 16:35:22</t>
         </is>
       </c>
-      <c r="L209" t="inlineStr"/>
-      <c r="M209" t="inlineStr"/>
-      <c r="N209" t="inlineStr"/>
-      <c r="O209" t="inlineStr"/>
-      <c r="P209" t="inlineStr"/>
-      <c r="Q209" t="inlineStr"/>
       <c r="R209" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -14309,12 +13061,6 @@
           <t>2026-06-24 16:35:23</t>
         </is>
       </c>
-      <c r="L210" t="inlineStr"/>
-      <c r="M210" t="inlineStr"/>
-      <c r="N210" t="inlineStr"/>
-      <c r="O210" t="inlineStr"/>
-      <c r="P210" t="inlineStr"/>
-      <c r="Q210" t="inlineStr"/>
       <c r="R210" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -14375,12 +13121,6 @@
           <t>2026-06-24 16:35:26</t>
         </is>
       </c>
-      <c r="L211" t="inlineStr"/>
-      <c r="M211" t="inlineStr"/>
-      <c r="N211" t="inlineStr"/>
-      <c r="O211" t="inlineStr"/>
-      <c r="P211" t="inlineStr"/>
-      <c r="Q211" t="inlineStr"/>
       <c r="R211" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -14441,12 +13181,6 @@
           <t>2026-06-24 16:35:27</t>
         </is>
       </c>
-      <c r="L212" t="inlineStr"/>
-      <c r="M212" t="inlineStr"/>
-      <c r="N212" t="inlineStr"/>
-      <c r="O212" t="inlineStr"/>
-      <c r="P212" t="inlineStr"/>
-      <c r="Q212" t="inlineStr"/>
       <c r="R212" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -14507,12 +13241,6 @@
           <t>2026-06-24 16:35:28</t>
         </is>
       </c>
-      <c r="L213" t="inlineStr"/>
-      <c r="M213" t="inlineStr"/>
-      <c r="N213" t="inlineStr"/>
-      <c r="O213" t="inlineStr"/>
-      <c r="P213" t="inlineStr"/>
-      <c r="Q213" t="inlineStr"/>
       <c r="R213" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -14573,12 +13301,6 @@
           <t>2026-06-24 16:35:29</t>
         </is>
       </c>
-      <c r="L214" t="inlineStr"/>
-      <c r="M214" t="inlineStr"/>
-      <c r="N214" t="inlineStr"/>
-      <c r="O214" t="inlineStr"/>
-      <c r="P214" t="inlineStr"/>
-      <c r="Q214" t="inlineStr"/>
       <c r="R214" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -14639,12 +13361,6 @@
           <t>2026-06-24 16:35:29</t>
         </is>
       </c>
-      <c r="L215" t="inlineStr"/>
-      <c r="M215" t="inlineStr"/>
-      <c r="N215" t="inlineStr"/>
-      <c r="O215" t="inlineStr"/>
-      <c r="P215" t="inlineStr"/>
-      <c r="Q215" t="inlineStr"/>
       <c r="R215" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -14705,12 +13421,6 @@
           <t>2026-06-24 16:35:31</t>
         </is>
       </c>
-      <c r="L216" t="inlineStr"/>
-      <c r="M216" t="inlineStr"/>
-      <c r="N216" t="inlineStr"/>
-      <c r="O216" t="inlineStr"/>
-      <c r="P216" t="inlineStr"/>
-      <c r="Q216" t="inlineStr"/>
       <c r="R216" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -14771,12 +13481,6 @@
           <t>2026-06-24 16:35:31</t>
         </is>
       </c>
-      <c r="L217" t="inlineStr"/>
-      <c r="M217" t="inlineStr"/>
-      <c r="N217" t="inlineStr"/>
-      <c r="O217" t="inlineStr"/>
-      <c r="P217" t="inlineStr"/>
-      <c r="Q217" t="inlineStr"/>
       <c r="R217" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -14837,12 +13541,6 @@
           <t>2026-06-24 16:35:32</t>
         </is>
       </c>
-      <c r="L218" t="inlineStr"/>
-      <c r="M218" t="inlineStr"/>
-      <c r="N218" t="inlineStr"/>
-      <c r="O218" t="inlineStr"/>
-      <c r="P218" t="inlineStr"/>
-      <c r="Q218" t="inlineStr"/>
       <c r="R218" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -14903,12 +13601,6 @@
           <t>2026-06-24 16:35:22</t>
         </is>
       </c>
-      <c r="L219" t="inlineStr"/>
-      <c r="M219" t="inlineStr"/>
-      <c r="N219" t="inlineStr"/>
-      <c r="O219" t="inlineStr"/>
-      <c r="P219" t="inlineStr"/>
-      <c r="Q219" t="inlineStr"/>
       <c r="R219" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -14969,12 +13661,6 @@
           <t>2026-06-24 16:35:36</t>
         </is>
       </c>
-      <c r="L220" t="inlineStr"/>
-      <c r="M220" t="inlineStr"/>
-      <c r="N220" t="inlineStr"/>
-      <c r="O220" t="inlineStr"/>
-      <c r="P220" t="inlineStr"/>
-      <c r="Q220" t="inlineStr"/>
       <c r="R220" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -15035,12 +13721,6 @@
           <t>2026-06-24 16:35:37</t>
         </is>
       </c>
-      <c r="L221" t="inlineStr"/>
-      <c r="M221" t="inlineStr"/>
-      <c r="N221" t="inlineStr"/>
-      <c r="O221" t="inlineStr"/>
-      <c r="P221" t="inlineStr"/>
-      <c r="Q221" t="inlineStr"/>
       <c r="R221" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -15101,12 +13781,6 @@
           <t>2026-06-24 16:35:37</t>
         </is>
       </c>
-      <c r="L222" t="inlineStr"/>
-      <c r="M222" t="inlineStr"/>
-      <c r="N222" t="inlineStr"/>
-      <c r="O222" t="inlineStr"/>
-      <c r="P222" t="inlineStr"/>
-      <c r="Q222" t="inlineStr"/>
       <c r="R222" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -15167,12 +13841,6 @@
           <t>2026-06-24 16:35:37</t>
         </is>
       </c>
-      <c r="L223" t="inlineStr"/>
-      <c r="M223" t="inlineStr"/>
-      <c r="N223" t="inlineStr"/>
-      <c r="O223" t="inlineStr"/>
-      <c r="P223" t="inlineStr"/>
-      <c r="Q223" t="inlineStr"/>
       <c r="R223" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -15233,12 +13901,6 @@
           <t>2026-06-24 16:35:40</t>
         </is>
       </c>
-      <c r="L224" t="inlineStr"/>
-      <c r="M224" t="inlineStr"/>
-      <c r="N224" t="inlineStr"/>
-      <c r="O224" t="inlineStr"/>
-      <c r="P224" t="inlineStr"/>
-      <c r="Q224" t="inlineStr"/>
       <c r="R224" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -15299,12 +13961,6 @@
           <t>2026-06-24 16:35:39</t>
         </is>
       </c>
-      <c r="L225" t="inlineStr"/>
-      <c r="M225" t="inlineStr"/>
-      <c r="N225" t="inlineStr"/>
-      <c r="O225" t="inlineStr"/>
-      <c r="P225" t="inlineStr"/>
-      <c r="Q225" t="inlineStr"/>
       <c r="R225" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -15365,12 +14021,6 @@
           <t>2026-06-24 16:35:39</t>
         </is>
       </c>
-      <c r="L226" t="inlineStr"/>
-      <c r="M226" t="inlineStr"/>
-      <c r="N226" t="inlineStr"/>
-      <c r="O226" t="inlineStr"/>
-      <c r="P226" t="inlineStr"/>
-      <c r="Q226" t="inlineStr"/>
       <c r="R226" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -15431,12 +14081,6 @@
           <t>2026-06-24 16:35:39</t>
         </is>
       </c>
-      <c r="L227" t="inlineStr"/>
-      <c r="M227" t="inlineStr"/>
-      <c r="N227" t="inlineStr"/>
-      <c r="O227" t="inlineStr"/>
-      <c r="P227" t="inlineStr"/>
-      <c r="Q227" t="inlineStr"/>
       <c r="R227" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -15497,12 +14141,6 @@
           <t>2026-06-24 16:35:43</t>
         </is>
       </c>
-      <c r="L228" t="inlineStr"/>
-      <c r="M228" t="inlineStr"/>
-      <c r="N228" t="inlineStr"/>
-      <c r="O228" t="inlineStr"/>
-      <c r="P228" t="inlineStr"/>
-      <c r="Q228" t="inlineStr"/>
       <c r="R228" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -15563,12 +14201,6 @@
           <t>2026-06-24 16:35:37</t>
         </is>
       </c>
-      <c r="L229" t="inlineStr"/>
-      <c r="M229" t="inlineStr"/>
-      <c r="N229" t="inlineStr"/>
-      <c r="O229" t="inlineStr"/>
-      <c r="P229" t="inlineStr"/>
-      <c r="Q229" t="inlineStr"/>
       <c r="R229" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -15629,12 +14261,6 @@
           <t>2026-06-24 16:35:46</t>
         </is>
       </c>
-      <c r="L230" t="inlineStr"/>
-      <c r="M230" t="inlineStr"/>
-      <c r="N230" t="inlineStr"/>
-      <c r="O230" t="inlineStr"/>
-      <c r="P230" t="inlineStr"/>
-      <c r="Q230" t="inlineStr"/>
       <c r="R230" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -15695,12 +14321,6 @@
           <t>2026-06-24 16:35:47</t>
         </is>
       </c>
-      <c r="L231" t="inlineStr"/>
-      <c r="M231" t="inlineStr"/>
-      <c r="N231" t="inlineStr"/>
-      <c r="O231" t="inlineStr"/>
-      <c r="P231" t="inlineStr"/>
-      <c r="Q231" t="inlineStr"/>
       <c r="R231" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -15761,12 +14381,6 @@
           <t>2026-06-24 16:35:47</t>
         </is>
       </c>
-      <c r="L232" t="inlineStr"/>
-      <c r="M232" t="inlineStr"/>
-      <c r="N232" t="inlineStr"/>
-      <c r="O232" t="inlineStr"/>
-      <c r="P232" t="inlineStr"/>
-      <c r="Q232" t="inlineStr"/>
       <c r="R232" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -15827,12 +14441,6 @@
           <t>2026-06-24 16:35:47</t>
         </is>
       </c>
-      <c r="L233" t="inlineStr"/>
-      <c r="M233" t="inlineStr"/>
-      <c r="N233" t="inlineStr"/>
-      <c r="O233" t="inlineStr"/>
-      <c r="P233" t="inlineStr"/>
-      <c r="Q233" t="inlineStr"/>
       <c r="R233" t="inlineStr">
         <is>
           <t>Miraee</t>
@@ -44306,7 +42914,6 @@
           <t>Tech View: Meet Leilani: Hawaii’s AI travel concierge - Honolulu Star-Advertiser</t>
         </is>
       </c>
-      <c r="I546" t="inlineStr"/>
       <c r="J546" t="inlineStr">
         <is>
           <t>Tuesday, June 30, 2026                                
@@ -46012,6 +44619,203 @@
         </is>
       </c>
     </row>
+    <row r="564">
+      <c r="A564" t="n">
+        <v>1162</v>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>Navan News</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/search?q=Navan+OR+TripActions+when:1d&amp;hl=en-US&amp;gl=US&amp;ceid=US:en</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>https://www.meathchronicle.ie/2026/07/01/navan-man-had-over-100-images-and-videos-of-child-abuse-material/</t>
+        </is>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>2026-07-01 09:55:26</t>
+        </is>
+      </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>Navan</t>
+        </is>
+      </c>
+      <c r="G564" t="inlineStr">
+        <is>
+          <t>Navan (Brand)</t>
+        </is>
+      </c>
+      <c r="H564" t="inlineStr">
+        <is>
+          <t>Navan man had over 100 images and videos of child abuse material - Meath Chronicle</t>
+        </is>
+      </c>
+      <c r="I564" t="inlineStr">
+        <is>
+          <t>Published:
+Wed 1 Jul 2026, 10:55 AM</t>
+        </is>
+      </c>
+      <c r="J564" t="inlineStr">
+        <is>
+          <t>A Navan man found with 104 images and videos of child sexual abuse imagery was previously deported from Canada for child luring, Trim Court heard.
+This was mentioned during the sentencing of John Casey (45), from 21 Hillview Navan who pleaded guilty to possession of child abuse material, also referred to as child pornography.
+Mr Casey was previously given a nine month prison sentence in Canada for attempting to groom or contact a male under the age of 16 and was deported from the country. He later changed his surname after this conviction.
+Detective Garda Jaime McKeown told the court an investigation began after Gardaí were notified of an Instagram page uploading and sharing child abusive material on 28th November 2021 and 16th May 2022.
+This led to a search being executed at Mr Casey’s address on 7th September 2022 where two phones and a tablet were seized. A total of 91 images and 13 videos of girls aged between 10 and 17 years old posing, engaging in sexual acts alone or with males, females or animals.
+The accused was arrested in November 2024 and interviewed at Navan Garda station where he maintained no comment in regards to the images. He pleaded guilty in court in February 2026.
+Judge John Martin noted how his previous conviction in Canada "doesn't seem to have deterred you”.
+Judge Martin also said the content of the child abuse material is “as base as it gets to be personally honest with you”.
+Defending barrister Paul Noctor told the court his client suffers from a serious car accident that happened when he was four years old that left him with a speech impediment. This affected his confidence and ability to gain employment.
+Bl Noctor told the court Casey is “a very lonely man,” who is suffering from depression and is currently on medication. The defending barrister said his client has an unhealthy addiction to pornography and realises now it is not a victimless crime. He has since installed blocks on his phone to stop him from downloading porn of any type and is making attempts to cure his addiction.
+Mr Casey was sentenced to two and a half years in prison with an additional six months suspended for 12 months and he will be on the sex offenders register indefinitely.</t>
+        </is>
+      </c>
+      <c r="K564" t="inlineStr">
+        <is>
+          <t>2026-07-01 13:41:58</t>
+        </is>
+      </c>
+      <c r="L564" t="inlineStr">
+        <is>
+          <t>Funding</t>
+        </is>
+      </c>
+      <c r="M564" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="N564" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O564" t="inlineStr">
+        <is>
+          <t>Navan executed funding movement impacting Miraee market segment</t>
+        </is>
+      </c>
+      <c r="P564" t="inlineStr">
+        <is>
+          <t>Moderate competitive movement. Assess Miraee's product positioning relative to Navan.</t>
+        </is>
+      </c>
+      <c r="Q564" t="inlineStr">
+        <is>
+          <t>A Navan man found with 104 images and videos of child sexual abuse imagery was previously deported from Canada for child luring, Trim Court heard. This was mentioned during the sentencing of John Casey (45), from 21 Hillview Navan who pleaded guilty to possession of child abuse material, also referred to as child pornography.</t>
+        </is>
+      </c>
+      <c r="R564" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="n">
+        <v>1163</v>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>Navan News</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/search?q=Navan+OR+TripActions+when:1d&amp;hl=en-US&amp;gl=US&amp;ceid=US:en</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>https://www.meathchronicle.ie/2026/07/01/man-charged-with-assault-causing-harm-at-navan-bar/</t>
+        </is>
+      </c>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>2026-07-01 10:58:21</t>
+        </is>
+      </c>
+      <c r="F565" t="inlineStr">
+        <is>
+          <t>Navan</t>
+        </is>
+      </c>
+      <c r="G565" t="inlineStr">
+        <is>
+          <t>Navan (Brand)</t>
+        </is>
+      </c>
+      <c r="H565" t="inlineStr">
+        <is>
+          <t>Man charged with assault causing harm at Navan bar - Meath Chronicle</t>
+        </is>
+      </c>
+      <c r="I565" t="inlineStr">
+        <is>
+          <t>Published:
+Wed 1 Jul 2026, 11:58 AM</t>
+        </is>
+      </c>
+      <c r="J565" t="inlineStr">
+        <is>
+          <t>Two people appeared in custody at Navan District Court in connection with alleged incidents in Navan and Ashbourne.
+Arturas Mauruca (36) with an address at Clonmagadden, Navan was charged with assault causing harm at The Watergate Bar and Kitchen, Watergate Street Navan on 21st June last. Detective Garda Conor McCluskey gave evidence of having arrested the accused at Blackcastle Demesne.
+He said he was taken to Navan Garda Station where he was charged. He was cautioned and made no reply to the caution. Judge Derek Cooney remanded him on €500 bail to appear at Trim District Court on 28th July next.
+Conditions of bail include notification of change of address to the Gardai, not to contact any witnesses by any means, surrender his passport a nd not to apply for travel documents and sign on at a Garda station three times a week.
+Separately, Shawna Moore (36) Huntsgrove, Ashbourne was charged with criminal damage of a hatch at Ashbourne Garda Station on 25th June last. It was alleged that she spat several times at the hetch.
+She was also charged with threatening, abusive and insulting behaviour and with intoxication in a public place. Garda Ulrike McKenzie  gave evidence of arrest. She was remanded o  bail back to Trim District Court next month.</t>
+        </is>
+      </c>
+      <c r="K565" t="inlineStr">
+        <is>
+          <t>2026-07-01 13:41:58</t>
+        </is>
+      </c>
+      <c r="L565" t="inlineStr">
+        <is>
+          <t>Product Launch</t>
+        </is>
+      </c>
+      <c r="M565" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="N565" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O565" t="inlineStr">
+        <is>
+          <t>Navan executed product launch movement impacting Miraee market segment</t>
+        </is>
+      </c>
+      <c r="P565" t="inlineStr">
+        <is>
+          <t>Standard market activity by Navan. No direct action required for Miraee.</t>
+        </is>
+      </c>
+      <c r="Q565" t="inlineStr">
+        <is>
+          <t>Two people appeared in custody at Navan District Court in connection with alleged incidents in Navan and Ashbourne. Arturas Mauruca (36) with an address at Clonmagadden, Navan was charged with assault causing harm at The Watergate Bar and Kitchen, Watergate Street Navan on 21st June last.</t>
+        </is>
+      </c>
+      <c r="R565" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/News_Intelligence/output/raw_news_database_Miraee.xlsx
+++ b/News_Intelligence/output/raw_news_database_Miraee.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R565"/>
+  <dimension ref="A1:R583"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44816,6 +44816,1720 @@
         </is>
       </c>
     </row>
+    <row r="566">
+      <c r="A566" t="n">
+        <v>1164</v>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>Navan News</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/search?q=Navan+OR+TripActions+when:1d&amp;hl=en-US&amp;gl=US&amp;ceid=US:en</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>https://www.gurufocus.com/news/8943172/navan-launches-model-context-protocol-mcp-for-travel-expense-management</t>
+        </is>
+      </c>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>2026-07-02 14:23:23</t>
+        </is>
+      </c>
+      <c r="F566" t="inlineStr">
+        <is>
+          <t>Navan</t>
+        </is>
+      </c>
+      <c r="G566" t="inlineStr">
+        <is>
+          <t>Navan (Brand)</t>
+        </is>
+      </c>
+      <c r="H566" t="inlineStr">
+        <is>
+          <t>Navan Launches Model Context Protocol (MCP) for Travel &amp; Expense Management - GuruFocus</t>
+        </is>
+      </c>
+      <c r="I566" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J566" t="inlineStr">
+        <is>
+          <t>[Summary Fallback] &lt;a href="https://news.google.com/rss/articles/CBMirwFBVV95cUxPMFFoNDNjcFN6b3hpR1c1cVp2VFpSZlllNW5rdFZrOU50NTYtOFF6RkgzSWxfR1dVdFVRSEpWZ3pGSjBEWWFUYVU2RUhkRGlCSUcwNDFNb083b1NPQzJ0TDlwZGxRRnhTdlhqREVwd3pIUm13ampvTlU4VmQtQlIycVlRbEZYN2JGYlVDWnNpQkRkLWlfMUZqZDJFT2JtNUJ5dzNETTVJSFF1LXJpSU1F?oc=5" target="_blank"&gt;Navan Launches Model Context Protocol (MCP) for Travel &amp; Expense Management&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;GuruFocus&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="K566" t="inlineStr">
+        <is>
+          <t>2026-07-02 16:03:40</t>
+        </is>
+      </c>
+      <c r="L566" t="inlineStr">
+        <is>
+          <t>Product Launch</t>
+        </is>
+      </c>
+      <c r="M566" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="N566" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O566" t="inlineStr">
+        <is>
+          <t>Navan executed product launch movement impacting Miraee market segment</t>
+        </is>
+      </c>
+      <c r="P566" t="inlineStr">
+        <is>
+          <t>Standard market activity by Navan. No direct action required for Miraee.</t>
+        </is>
+      </c>
+      <c r="Q566" t="inlineStr">
+        <is>
+          <t>Navan Launches Model Context Protocol (MCP) for Travel &amp; Expense Management&amp;nbsp;&amp;nbsp;GuruFocus.</t>
+        </is>
+      </c>
+      <c r="R566" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="n">
+        <v>1165</v>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>Navan News</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/search?q=Navan+OR+TripActions+when:1d&amp;hl=en-US&amp;gl=US&amp;ceid=US:en</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>https://www.investing.com/news/company-news/navan-launches-protocol-to-connect-ai-tools-with-travel-data-93CH-4773223</t>
+        </is>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:25:51</t>
+        </is>
+      </c>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>Navan</t>
+        </is>
+      </c>
+      <c r="G567" t="inlineStr">
+        <is>
+          <t>Navan (Brand)</t>
+        </is>
+      </c>
+      <c r="H567" t="inlineStr">
+        <is>
+          <t>Navan launches protocol to connect AI tools with travel data - Investing.com</t>
+        </is>
+      </c>
+      <c r="I567" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J567" t="inlineStr">
+        <is>
+          <t>[Summary Fallback] &lt;a href="https://news.google.com/rss/articles/CBMiuAFBVV95cUxPUUVEU1BIcEVodGtVZXJVZ3N2emlDV1FCSkZidkRYVDVJTjk4NElQY2xWOHdMdkItYXI1YkZMNlBPZDg2d0JXQmVINndfMnAxdVpWWjhoX2ZpdlpidDVLby1LbmxxdDZkMXNBYVAwY0swb1ludTZmN0lQWnQySXY5ZEMzZmx1TDJMOU9fOWYyZEhYaXV5Q3dCWnU3N0szT1JGZEw5R1Z5VEN4MzFaV294aFNQNG1zQl9V?oc=5" target="_blank"&gt;Navan launches protocol to connect AI tools with travel data&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Investing.com&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="K567" t="inlineStr">
+        <is>
+          <t>2026-07-02 16:03:40</t>
+        </is>
+      </c>
+      <c r="L567" t="inlineStr">
+        <is>
+          <t>Funding</t>
+        </is>
+      </c>
+      <c r="M567" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="N567" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O567" t="inlineStr">
+        <is>
+          <t>Navan executed funding movement impacting Miraee market segment</t>
+        </is>
+      </c>
+      <c r="P567" t="inlineStr">
+        <is>
+          <t>Standard market activity by Navan. No direct action required for Miraee.</t>
+        </is>
+      </c>
+      <c r="Q567" t="inlineStr">
+        <is>
+          <t>Navan launches protocol to connect AI tools with travel data&amp;nbsp;&amp;nbsp;Investing.</t>
+        </is>
+      </c>
+      <c r="R567" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="n">
+        <v>1166</v>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>Navan News</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/search?q=Navan+OR+TripActions+when:1d&amp;hl=en-US&amp;gl=US&amp;ceid=US:en</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>https://www.railwaygazette.com/ireland/2026/07/02/consultation-extended-for-project-to-reinstate-railway-to-navan/</t>
+        </is>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>2026-07-02 10:00:03</t>
+        </is>
+      </c>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>Navan</t>
+        </is>
+      </c>
+      <c r="G568" t="inlineStr">
+        <is>
+          <t>Navan (Brand)</t>
+        </is>
+      </c>
+      <c r="H568" t="inlineStr">
+        <is>
+          <t>Consultation underway for project to reinstate railway to Navan - Railway Gazette International</t>
+        </is>
+      </c>
+      <c r="I568" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J568" t="inlineStr">
+        <is>
+          <t>[Summary Fallback] &lt;a href="https://news.google.com/rss/articles/CBMitAFBVV95cUxPVFpGMFlsYXJDdGlYVzNOeEFnSExHbXBReEVnQWNvQmZ2UFpIODg4eWl4NW5jZjZmc2lFMTBHRUxOVnVha29KanRLNmJvZ243cW5CZkdJTzhmbTMwTld3dWVsREhidE52alNwWC12d2FpanY0aGVNQTV5eWhWUkw5NlNZT082OWFMd1EySVVfSXp0ZFBGT1BRazltemQtS2pIdEZGU1Q2N2RQTXdLY2dlY0E5LTk?oc=5" target="_blank"&gt;Consultation underway for project to reinstate railway to Navan&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Railway Gazette International&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="K568" t="inlineStr">
+        <is>
+          <t>2026-07-02 16:03:40</t>
+        </is>
+      </c>
+      <c r="L568" t="inlineStr">
+        <is>
+          <t>General Travel News</t>
+        </is>
+      </c>
+      <c r="M568" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="N568" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O568" t="inlineStr">
+        <is>
+          <t>Navan executed general travel news movement impacting Miraee market segment</t>
+        </is>
+      </c>
+      <c r="P568" t="inlineStr">
+        <is>
+          <t>Standard market activity by Navan. No direct action required for Miraee.</t>
+        </is>
+      </c>
+      <c r="Q568" t="inlineStr">
+        <is>
+          <t>Consultation underway for project to reinstate railway to Navan&amp;nbsp;&amp;nbsp;Railway Gazette International.</t>
+        </is>
+      </c>
+      <c r="R568" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="n">
+        <v>1167</v>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>Navan News</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/search?q=Navan+OR+TripActions+when:1d&amp;hl=en-US&amp;gl=US&amp;ceid=US:en</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>https://ng.investing.com/news/stock-market-news/earnings-call-transcript-navan-inc-q1-2027-shows-strong-growth-but-stock-dips-93CH-2552952</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>2026-07-01 21:18:11</t>
+        </is>
+      </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>Navan</t>
+        </is>
+      </c>
+      <c r="G569" t="inlineStr">
+        <is>
+          <t>Navan (Brand)</t>
+        </is>
+      </c>
+      <c r="H569" t="inlineStr">
+        <is>
+          <t>Earnings call transcript: Navan Inc. Q1 2027 shows strong growth, stock rises nearly 20% - Investing.com Nigeria</t>
+        </is>
+      </c>
+      <c r="I569" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J569" t="inlineStr">
+        <is>
+          <t>[Summary Fallback] &lt;a href="https://news.google.com/rss/articles/CBMi1AFBVV95cUxPc0Y4SmdkSE9od3VtODBSTy1VUHlCNDdKNGlmRTAzMnE3Z0JINlQ5ZkNfYndta1RYenZLZHVzZUpBNUd3ZnBHRTh3SXQyc29DZzNkS09FNEQwUUltZW5ua2pxOXBCV2YyemdiRkJwLXhqTHNtX1owZGJDZTc2TkJ4SUhHWmhUQUJ3VmFFakYwQkxjeEh5LWlveEZYb0M0eWItN1dhRkx6bEZ0UlRDSE55U2QtbGNSM3JJcUhMcG95cDhZOThOVVFyNmpLS2VHUmNqSTVIMQ?oc=5" target="_blank"&gt;Earnings call transcript: Navan Inc. Q1 2027 shows strong growth, stock rises nearly 20%&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Investing.com Nigeria&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="K569" t="inlineStr">
+        <is>
+          <t>2026-07-02 16:03:40</t>
+        </is>
+      </c>
+      <c r="L569" t="inlineStr">
+        <is>
+          <t>Funding</t>
+        </is>
+      </c>
+      <c r="M569" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="N569" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O569" t="inlineStr">
+        <is>
+          <t>Navan executed funding movement impacting Miraee market segment</t>
+        </is>
+      </c>
+      <c r="P569" t="inlineStr">
+        <is>
+          <t>Moderate competitive movement. Assess Miraee's product positioning relative to Navan.</t>
+        </is>
+      </c>
+      <c r="Q569" t="inlineStr">
+        <is>
+          <t>Earnings call transcript: Navan Inc. Q1 2027 shows strong growth, stock rises nearly 20%&amp;nbsp;&amp;nbsp;Investing.</t>
+        </is>
+      </c>
+      <c r="R569" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="n">
+        <v>1168</v>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>Navan News</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/search?q=Navan+OR+TripActions+when:1d&amp;hl=en-US&amp;gl=US&amp;ceid=US:en</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>https://ca.investing.com/news/stock-market-news/form-144-navan-for-1-july-93CH-4717085</t>
+        </is>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>2026-07-01 20:47:06</t>
+        </is>
+      </c>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>Navan</t>
+        </is>
+      </c>
+      <c r="G570" t="inlineStr">
+        <is>
+          <t>Navan (Brand)</t>
+        </is>
+      </c>
+      <c r="H570" t="inlineStr">
+        <is>
+          <t>Form 144 NAVAN For: 1 July By Investing.com - Investing.com Canada</t>
+        </is>
+      </c>
+      <c r="I570" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J570" t="inlineStr">
+        <is>
+          <t>[Summary Fallback] &lt;a href="https://news.google.com/rss/articles/CBMijwFBVV95cUxNT251OGItUzhOSURZM2JGUXVXTFV5X3hzalNLR3dqSmozLVFxQ3ZHVU5yVm02eXg0eXpJWlRPVTU0T0RleHMtNzZxajkzemMtdlVEUFFRN1RmdFp1QVJBN0RYaENNUEVfTHEwUkdaQ3NGVV84eXlDVXByd0F4WGlyMzhadF9Kb3FtQkdpNGJibw?oc=5" target="_blank"&gt;Form 144 NAVAN For: 1 July By Investing.com&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Investing.com Canada&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="K570" t="inlineStr">
+        <is>
+          <t>2026-07-02 16:03:40</t>
+        </is>
+      </c>
+      <c r="L570" t="inlineStr">
+        <is>
+          <t>Funding</t>
+        </is>
+      </c>
+      <c r="M570" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="N570" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O570" t="inlineStr">
+        <is>
+          <t>Navan executed funding movement impacting Miraee market segment</t>
+        </is>
+      </c>
+      <c r="P570" t="inlineStr">
+        <is>
+          <t>Standard market activity by Navan. No direct action required for Miraee.</t>
+        </is>
+      </c>
+      <c r="Q570" t="inlineStr">
+        <is>
+          <t>Form 144 NAVAN For: 1 July By Investing. com&amp;nbsp;&amp;nbsp;Investing.</t>
+        </is>
+      </c>
+      <c r="R570" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="n">
+        <v>1169</v>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>Brex News</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/search?q=Brex+when:1d&amp;hl=en-US&amp;gl=US&amp;ceid=US:en</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>https://mshale.com/a61eaa12/ac41e537qVv0N3jF6sc</t>
+        </is>
+      </c>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>2026-07-02 11:47:51</t>
+        </is>
+      </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="G571" t="inlineStr">
+        <is>
+          <t>Brex (Brand)</t>
+        </is>
+      </c>
+      <c r="H571" t="inlineStr">
+        <is>
+          <t>Utsunomiya Brex Vs. Levanga Hokkaido - Condensed Game Cristiano Ronaldo (0UlVBjKL8D) - Mshale</t>
+        </is>
+      </c>
+      <c r="I571" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J571" t="inlineStr">
+        <is>
+          <t>[Summary Fallback] &lt;a href="https://news.google.com/rss/articles/CBMiW0FVX3lxTFBzako4YWVVYVg5VmMzSHZKMDFyeUVFZWsycG1KWlFkUlJBZ1V2V3lHQmtSZnp2MVlRdGlYc1BDa211U0tES1FJaU9SNlJnYjZ2ak9XY2R0b28xbms?oc=5" target="_blank"&gt;Utsunomiya Brex Vs. Levanga Hokkaido - Condensed Game Cristiano Ronaldo (0UlVBjKL8D)&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Mshale&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="K571" t="inlineStr">
+        <is>
+          <t>2026-07-02 16:03:40</t>
+        </is>
+      </c>
+      <c r="L571" t="inlineStr">
+        <is>
+          <t>General Travel News</t>
+        </is>
+      </c>
+      <c r="M571" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="N571" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O571" t="inlineStr">
+        <is>
+          <t>Brex executed general travel news movement impacting Miraee market segment</t>
+        </is>
+      </c>
+      <c r="P571" t="inlineStr">
+        <is>
+          <t>Standard market activity by Brex. No direct action required for Miraee.</t>
+        </is>
+      </c>
+      <c r="Q571" t="inlineStr">
+        <is>
+          <t>Utsunomiya Brex Vs. Levanga Hokkaido - Condensed Game Cristiano Ronaldo (0UlVBjKL8D)&amp;nbsp;&amp;nbsp;Mshale.</t>
+        </is>
+      </c>
+      <c r="R571" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="n">
+        <v>1170</v>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>Brex News</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/search?q=Brex+when:1d&amp;hl=en-US&amp;gl=US&amp;ceid=US:en</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>https://mshale.com/096a7372/fe3e2275AzU5FC4NQU4-PSw</t>
+        </is>
+      </c>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>2026-07-02 07:50:41</t>
+        </is>
+      </c>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="G572" t="inlineStr">
+        <is>
+          <t>Brex (Brand)</t>
+        </is>
+      </c>
+      <c r="H572" t="inlineStr">
+        <is>
+          <t>Sunrockers Shibuya Vs. Utsunomiya Brex - Condensed Game Alaves Barcellona (RPv0YnljBl) - Mshale</t>
+        </is>
+      </c>
+      <c r="I572" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J572" t="inlineStr">
+        <is>
+          <t>[Summary Fallback] &lt;a href="https://news.google.com/rss/articles/CBMiYEFVX3lxTE5BRHhCbHdhSWd5WmVCcW9nTmxjeTE1Qm81LVlOMzdtalQ3QXJFR0cyaDhnQ29aTW5ZM0hLVmFTb0o3S1ZNaWNjYk5zUnpMLUZ1RGJFUjBZODIyU2ZUZ3BqZA?oc=5" target="_blank"&gt;Sunrockers Shibuya Vs. Utsunomiya Brex - Condensed Game Alaves Barcellona (RPv0YnljBl)&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Mshale&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="K572" t="inlineStr">
+        <is>
+          <t>2026-07-02 16:03:40</t>
+        </is>
+      </c>
+      <c r="L572" t="inlineStr">
+        <is>
+          <t>General Travel News</t>
+        </is>
+      </c>
+      <c r="M572" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="N572" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O572" t="inlineStr">
+        <is>
+          <t>Brex executed general travel news movement impacting Miraee market segment</t>
+        </is>
+      </c>
+      <c r="P572" t="inlineStr">
+        <is>
+          <t>Standard market activity by Brex. No direct action required for Miraee.</t>
+        </is>
+      </c>
+      <c r="Q572" t="inlineStr">
+        <is>
+          <t>Sunrockers Shibuya Vs. Utsunomiya Brex - Condensed Game Alaves Barcellona (RPv0YnljBl)&amp;nbsp;&amp;nbsp;Mshale.</t>
+        </is>
+      </c>
+      <c r="R572" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="n">
+        <v>1171</v>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>Brex News</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/search?q=Brex+when:1d&amp;hl=en-US&amp;gl=US&amp;ceid=US:en</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>https://mshale.com/215344e8/e996b72bm1fBQQCJWX0</t>
+        </is>
+      </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>2026-07-02 08:18:35</t>
+        </is>
+      </c>
+      <c r="F573" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="G573" t="inlineStr">
+        <is>
+          <t>Brex (Brand)</t>
+        </is>
+      </c>
+      <c r="H573" t="inlineStr">
+        <is>
+          <t>SHIGA LAKES Vs UTSUNOMIYA BREX | 2026-03-14 | RESONA GROUP B.LEAGUE 2025-26 Humberto Cruz (7yFsEPH5YY) - Mshale</t>
+        </is>
+      </c>
+      <c r="I573" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J573" t="inlineStr">
+        <is>
+          <t>[Summary Fallback] &lt;a href="https://news.google.com/rss/articles/CBMiW0FVX3lxTFA3enpWci1KekktdUxtSjgwUjBPUnJlMWR3RWJMNllMRVdaSlB3cUpDQzZSaUt4Z3d3Zm80ZzdKajZyaXgxQlVrajEwcnZHQlZjbmhZRk94NjZxVTA?oc=5" target="_blank"&gt;SHIGA LAKES Vs UTSUNOMIYA BREX | 2026-03-14 | RESONA GROUP B.LEAGUE 2025-26 Humberto Cruz (7yFsEPH5YY)&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Mshale&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="K573" t="inlineStr">
+        <is>
+          <t>2026-07-02 16:03:40</t>
+        </is>
+      </c>
+      <c r="L573" t="inlineStr">
+        <is>
+          <t>General Travel News</t>
+        </is>
+      </c>
+      <c r="M573" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="N573" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O573" t="inlineStr">
+        <is>
+          <t>Brex executed general travel news movement impacting Miraee market segment</t>
+        </is>
+      </c>
+      <c r="P573" t="inlineStr">
+        <is>
+          <t>Standard market activity by Brex. No direct action required for Miraee.</t>
+        </is>
+      </c>
+      <c r="Q573" t="inlineStr">
+        <is>
+          <t>SHIGA LAKES Vs UTSUNOMIYA BREX | 2026-03-14 | RESONA GROUP B. LEAGUE 2025-26 Humberto Cruz (7yFsEPH5YY)&amp;nbsp;&amp;nbsp;Mshale.</t>
+        </is>
+      </c>
+      <c r="R573" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="n">
+        <v>1172</v>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>Brex News</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/search?q=Brex+when:1d&amp;hl=en-US&amp;gl=US&amp;ceid=US:en</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>https://mshale.com/39784ee1/d0768aa0cyQPsdJUlJY</t>
+        </is>
+      </c>
+      <c r="E574" t="inlineStr">
+        <is>
+          <t>2026-07-02 00:45:33</t>
+        </is>
+      </c>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="G574" t="inlineStr">
+        <is>
+          <t>Brex (Brand)</t>
+        </is>
+      </c>
+      <c r="H574" t="inlineStr">
+        <is>
+          <t>Game Highlights: Taoyuan Pauian Pilots Vs Utsunomiya Brex (Championship) | EASL Finals Macau 2026 Alex Caruso (NzABTiUIf4) - Mshale</t>
+        </is>
+      </c>
+      <c r="I574" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J574" t="inlineStr">
+        <is>
+          <t>[Summary Fallback] &lt;a href="https://news.google.com/rss/articles/CBMiW0FVX3lxTFA2aTBRdDR5UzdUa0hpWFhKNl9sZ01jOTBSRF9TQ3h5RllVWTJfUG9QVWR5Qk5ibmlrRzlTbnZFbHVZN1ljRk1idnJwdGxOaHp1S2ZrWEdxZXQ0YTA?oc=5" target="_blank"&gt;Game Highlights: Taoyuan Pauian Pilots Vs Utsunomiya Brex (Championship) | EASL Finals Macau 2026 Alex Caruso (NzABTiUIf4)&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Mshale&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="K574" t="inlineStr">
+        <is>
+          <t>2026-07-02 16:03:40</t>
+        </is>
+      </c>
+      <c r="L574" t="inlineStr">
+        <is>
+          <t>General Travel News</t>
+        </is>
+      </c>
+      <c r="M574" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="N574" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O574" t="inlineStr">
+        <is>
+          <t>Brex executed general travel news movement impacting Miraee market segment</t>
+        </is>
+      </c>
+      <c r="P574" t="inlineStr">
+        <is>
+          <t>Standard market activity by Brex. No direct action required for Miraee.</t>
+        </is>
+      </c>
+      <c r="Q574" t="inlineStr">
+        <is>
+          <t>Game Highlights: Taoyuan Pauian Pilots Vs Utsunomiya Brex (Championship) | EASL Finals Macau 2026 Alex Caruso (NzABTiUIf4)&amp;nbsp;&amp;nbsp;Mshale.</t>
+        </is>
+      </c>
+      <c r="R574" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="n">
+        <v>1173</v>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>Navan News</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/search?q=Navan+OR+TripActions+when:1d&amp;hl=en-US&amp;gl=US&amp;ceid=US:en</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>https://www.indexbox.io/blog/iarnrd-ireann-launches-public-consultation-for-navan-railway-restoration/</t>
+        </is>
+      </c>
+      <c r="E575" t="inlineStr">
+        <is>
+          <t>2026-07-02 11:12:00</t>
+        </is>
+      </c>
+      <c r="F575" t="inlineStr">
+        <is>
+          <t>Navan</t>
+        </is>
+      </c>
+      <c r="G575" t="inlineStr">
+        <is>
+          <t>Navan (Brand)</t>
+        </is>
+      </c>
+      <c r="H575" t="inlineStr">
+        <is>
+          <t>Navan Railway Restoration: Public Consultation Extended to July 17, 2026 - News and Statistics - IndexBox</t>
+        </is>
+      </c>
+      <c r="I575" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J575" t="inlineStr">
+        <is>
+          <t>Iarnród Éireann has initiated a public consultation process for a scheme to restore a railway link to Navan, with the National Transport Authority unveiling the emerging preferred route for a 34 km electrified line serving what is noted as Ireland's largest town lacking a rail connection.
+The original consultation cutoff of July 3 has been pushed back by two weeks to July 17, responding to input from stakeholders. The Navan railway ceased operations in 1963, following the end of passenger services in 1947. The initial phase of restoration was finished in 2013, featuring a 7.5 km branch from the Maynooth line running from Clonsilla to M3 Parkway at Pace near Dunboyne.
+Government approval for the second phase, which extends the line to Navan, came in January 2023, with an anticipated opening in 2036. The €750 million initiative is part of the greater Dublin area transport strategy and would enable direct DART suburban rail services connecting Dublin Connolly and Navan.
+The chosen route largely follows the path of the line shut down in 1963, with adjustments to better accommodate the expanding commuter hub of Dunshaughlin and to bypass a cycling and pedestrian Greenway occupying the former railway. Proposed stations include Dunshaughlin, Kilmessan, Navan Central, and Navan North, with park-and-ride facilities slated for all except Navan Central.
+During peak periods, trains would run as frequently as every 15 minutes, with a travel time from Navan to Dublin of roughly 60 minutes. This setup would offer capacity for up to 4,400 passengers per direction per hour.
+Transport Minister Darragh O'Brien stated that, as the largest town in Ireland without a railway service, this new line will address significant commuter demand from Navan and, via new park-and-ride sites, from more distant areas. National Transport Authority Chief Executive Anne Shaw called the project transformative for County Meath and the broader Greater Dublin Area, reconnecting Navan and nearby communities to the national rail network and delivering a high-capacity, sustainable alternative to driving.
+Input from the public consultation, additional design work, and environmental assessments will be weighed before the preferred route is finalized. A Railway Order application will then be filed with An Coimisiún Pleanála, the national independent planning authority.
+Making Data-Driven Decisions to Grow Your Business
+A Quick Overview of Market Performance
+Understanding the Current State of The Market and its Prospects
+Finding New Products to Diversify Your Business
+Choosing the Best Countries to Establish Your Sustainable Supply Chain
+Choosing the Best Countries to Boost Your Export
+The Latest Trends and Insights into The Industry
+The Largest Import Supplying Countries
+The Largest Destinations for Exports
+The Largest Producers on The Market and Their Profiles
+The Largest Markets And Their Profiles
+Instant access. No credit card needed.
+Online access to 2M+ reports, dashboards, and tables. Trusted by Fortune 500 teams.</t>
+        </is>
+      </c>
+      <c r="K575" t="inlineStr">
+        <is>
+          <t>2026-07-02 16:03:40</t>
+        </is>
+      </c>
+      <c r="L575" t="inlineStr">
+        <is>
+          <t>Product Launch</t>
+        </is>
+      </c>
+      <c r="M575" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="N575" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O575" t="inlineStr">
+        <is>
+          <t>Navan executed product launch movement impacting Miraee market segment</t>
+        </is>
+      </c>
+      <c r="P575" t="inlineStr">
+        <is>
+          <t>High competitive activity. Monitor Navan's product launch closely and evaluate defense strategies for Miraee.</t>
+        </is>
+      </c>
+      <c r="Q575" t="inlineStr">
+        <is>
+          <t>Iarnród Éireann has initiated a public consultation process for a scheme to restore a railway link to Navan, with the National Transport Authority unveiling the emerging preferred route for a 34 km electrified line serving what is noted as Ireland's largest town lacking a rail connection. The original consultation cutoff of July 3 has been pushed back by two weeks to July 17, responding to input from stakeholders.</t>
+        </is>
+      </c>
+      <c r="R575" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="n">
+        <v>1174</v>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>Navan News</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/search?q=Navan+OR+TripActions+when:1d&amp;hl=en-US&amp;gl=US&amp;ceid=US:en</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>https://www.tipranks.com/news/catalyst/navan-soars-after-landing-major-cummins-deal</t>
+        </is>
+      </c>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>2026-07-01 18:28:07</t>
+        </is>
+      </c>
+      <c r="F576" t="inlineStr">
+        <is>
+          <t>Navan</t>
+        </is>
+      </c>
+      <c r="G576" t="inlineStr">
+        <is>
+          <t>Navan (Brand)</t>
+        </is>
+      </c>
+      <c r="H576" t="inlineStr">
+        <is>
+          <t>Navan Soars After Landing Major Cummins Deal - TipRanks</t>
+        </is>
+      </c>
+      <c r="I576" t="inlineStr">
+        <is>
+          <t>/news/author/tipranksbreakingnews</t>
+        </is>
+      </c>
+      <c r="J576" t="inlineStr">
+        <is>
+          <t>Navan, Inc. Class A ( (NAVN) ) is experiencing volatility. Read on for a possible explanation for the stockâs unusual movement.
+Navan, Inc. is rallying as investors cheer news that engine maker Cummins has chosen its platform to run global business travel, a marquee contract that validates Navanâs standing with blueâchip customers. The move builds on a strong fiscal firstâquarter report, where the company beat revenue expectations and raised its fullâyear outlook, reinforcing confidence in its AIâdriven travel and expense tools.
+Supporters say Navanâs rapid growth in bookings and revenue suggests its software is catching on with more customers, giving it a bigger base to profit from over time. Still, the companyâs sizable GAAP losses and negative margins remain a key overhang, as ongoing red ink could weigh on sentiment if Navan fails to turn scale and efficiency gains into durable bottomâline profits.
+More about Navan, Inc. Class A
+YTD Price Performance: 33.90%
+Average Trading Volume: 4,004,084
+Technical Sentiment Signal: Strong Buy
+Current Market Cap: $5.82B
+For further insights into NAVN stock on
+TipRanksâ Stock Analysis page.
+See more of todayâs
+top stock gainers and losers.
+Disclaimer &amp; DisclosureReport an Issue</t>
+        </is>
+      </c>
+      <c r="K576" t="inlineStr">
+        <is>
+          <t>2026-07-02 16:03:40</t>
+        </is>
+      </c>
+      <c r="L576" t="inlineStr">
+        <is>
+          <t>Funding</t>
+        </is>
+      </c>
+      <c r="M576" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="N576" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O576" t="inlineStr">
+        <is>
+          <t>Navan executed funding movement impacting Miraee market segment</t>
+        </is>
+      </c>
+      <c r="P576" t="inlineStr">
+        <is>
+          <t>Standard market activity by Navan. No direct action required for Miraee.</t>
+        </is>
+      </c>
+      <c r="Q576" t="inlineStr">
+        <is>
+          <t>Navan, Inc. Class A ( (NAVN) ) is experiencing volatility.</t>
+        </is>
+      </c>
+      <c r="R576" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="n">
+        <v>1175</v>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>Navan News</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/search?q=Navan+OR+TripActions+when:1d&amp;hl=en-US&amp;gl=US&amp;ceid=US:en</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>https://www.thetraveler.org/public-consultation-opens-on-navan-railway-reinstatement/</t>
+        </is>
+      </c>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>2026-07-02 11:06:31</t>
+        </is>
+      </c>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t>Navan</t>
+        </is>
+      </c>
+      <c r="G577" t="inlineStr">
+        <is>
+          <t>Navan (Brand)</t>
+        </is>
+      </c>
+      <c r="H577" t="inlineStr">
+        <is>
+          <t>Public consultation opens on Navan railway reinstatement - thetraveler.org</t>
+        </is>
+      </c>
+      <c r="I577" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J577" t="inlineStr">
+        <is>
+          <t>More news on this day
+Plans to reinstate a railway connection to Navan have moved into a crucial new phase, with a public consultation now underway on the emerging preferred route for a new line linking the County Meath town to Dublin via M3 Parkway.
+Get the latest news straight to your inbox!
+Publicly available information from Iarnród Éireann shows that the proposed Navan Railway would extend the existing commuter network from M3 Parkway, creating a largely double-track, electrified line designed to carry high frequency DART-style services between Navan and Dublin. Project documents describe the scheme as a key element of the Greater Dublin Area Transport Strategy 2022 to 2042, intended to shift more trips from private cars to public transport along the rapidly growing Navan corridor.
+The emerging preferred route presented for consultation identifies a sequence of new and upgraded stations between M3 Parkway and Navan, together with park-and-ride facilities and connections to local bus and walking and cycling networks. A new Navan Central station is envisaged close to lands already highlighted in Meath County Council planning reports as strategic for town centre expansion and future rail access. Other stops would serve communities such as Dunshaughlin and Kilmessan, aiming to bring a wider catchment within reach of rail.
+Project material indicates that journey times of around one hour between Navan and Dublin city centre are being targeted, with capacity for thousands of passengers in each direction at peak periods. The line is planned to integrate with the broader DART+ programme so that trains from Navan would run through to key Dublin hubs without requiring transfers, placing the town more firmly within the capital’s commuter belt.
+The consultation documentation also outlines a programme of associated works, including new bridges, level crossing changes and railway earthworks. While detailed cost estimates are not published at this stage, previous assessments by the National Transport Authority have indicated that construction of a Navan rail link would represent a multibillion-euro investment over the life of the project.
+According to Irish Rail project information, the non-statutory public consultation on the emerging preferred route opened in late May 2026 and is scheduled to run until the afternoon of Friday 3 July 2026. During this period, residents, businesses, community groups and other stakeholders along the corridor are being invited to submit views on the route, station locations and potential environmental and community impacts.
+The consultation is structured around a series of in-person information events in Navan, Dunshaughlin and Kilmessan, alongside an online webinar and digital feedback forms. Project staff are available at these sessions to explain route drawings and environmental constraints maps, helping attendees understand how different options have been assessed. The format is intended to capture both local concerns and suggestions on issues such as access, noise, visual impact and opportunities for complementary public realm improvements.
+Reports from local media and advocacy groups indicate strong interest in the process, reflecting the long-running debate around rail provision to Navan. Campaigners who have lobbied for reinstatement of passenger services for many years are using the consultation window to press for timely delivery, while others are focusing on how the alignment interacts with existing housing, roads and green spaces.
+The current exercise is described as a non-statutory consultation ahead of a future application for a Railway Order, the Irish planning consent for major rail projects. Subject to feedback and government approvals, Irish Rail expects to refine the design and environmental assessments before entering the formal planning stage toward the end of this decade.
+The move into public consultation comes against a backdrop of sustained population and employment growth in County Meath and the broader Dublin commuter belt. Official transport planning documents identify the Navan to Dublin corridor as a priority for investment, citing rising road congestion on the M3 motorway and strong demand on existing bus services linking the town to the capital.
+Data published by the National Transport Authority on the Navan to Dublin NX bus route shows passenger numbers increasing significantly since 2019, with patronage in late 2025 reported to be around half again higher than pre-pandemic levels. In parallel, the authority has launched its own consultation on proposed enhancements to the NX service, underscoring how rail and bus improvements are being developed in tandem as part of a wider sustainable transport package.
+The draft All-Island Strategic Rail Review and the Greater Dublin Area Transport Strategy both position the Navan line as part of a long-term rebalancing of Ireland’s transport network, with an emphasis on electrified rail corridors radiating from Dublin. The proposed extension of DART services to Navan would complement other planned projects such as DART+ West and DART+ Coastal, which aim to increase capacity and frequency for rail commuters across the metropolitan area.
+Local planning initiatives are also being shaped around the prospect of rail reinstatement. Meath County Council has previously consulted on a masterplan for lands earmarked for the expansion of Navan town centre, noting their potential role as a site for a future central rail station. Observers suggest that aligning land use plans with the rail project could support higher density, transit-oriented development within walking distance of the new station.
+While there is broad recognition in policy documents that a reinstated rail line to Navan could bring environmental and economic benefits, the specifics of the emerging preferred route are already generating detailed debate. Some of this discussion focuses on how closely the new alignment should follow the existing freight corridor used to serve Tara Mines and sections of the former Kingscourt line, and where exactly to locate stations to balance accessibility with construction costs.
+Active travel advocates are using the consultation to argue for integrated cycling and walking infrastructure alongside the railway. Navan Cycling Initiative, for example, has publicly called for a continuous greenway corridor to run parallel to the line where feasible, contending that such an approach would maximise the benefits of the investment by creating a car-free spine for local trips as well as regional commuting.
+Others are raising concerns about potential loss of amenity where the line passes close to existing homes or recreational spaces, and about how construction traffic and works compounds might affect communities during the build period. The consultation materials outline proposed mitigation measures, but detailed commitments on noise barriers, landscaping and access changes will be developed further as design progresses.
+Environmental assessments will consider issues such as impacts on waterways, biodiversity and floodplains along the route, and how the project can align with national climate goals. Stakeholders are being encouraged to identify local environmental sensitivities that may not be fully captured in regional datasets, so that they can be taken into account before a final route is fixed.
+Once the consultation closes in July, Irish Rail has indicated that it will review submissions and publish a report summarising the main themes and proposed responses. The emerging preferred route may be refined to reflect feedback, especially where alternative local alignments or station access arrangements are put forward by communities or landowners.
+Subsequent stages will involve detailed design, environmental impact assessment and preparation of a Railway Order application to An Bord Pleanála. National Transport Authority responses to parliamentary questions in recent years have referred to an indicative timeline in which an application would be lodged toward the latter part of the decade, with construction and commissioning extending into the 2030s, although precise dates remain subject to funding decisions and statutory approvals.
+For now, transport planners and local stakeholders see the current consultation as a significant milestone in a project that has been discussed for decades. The outcome will help determine the final shape of the reinstated Navan railway, including which communities gain direct station access, how the line fits with bus and active travel networks, and how its impacts on landscapes and neighbourhoods are managed.
+With both national strategies and local development plans increasingly geared toward reducing car dependence, the consultation period represents a critical opportunity for residents of Navan and the wider corridor to influence the design of a rail link that could reshape daily travel patterns for generations to come.</t>
+        </is>
+      </c>
+      <c r="K577" t="inlineStr">
+        <is>
+          <t>2026-07-02 16:03:40</t>
+        </is>
+      </c>
+      <c r="L577" t="inlineStr">
+        <is>
+          <t>Funding</t>
+        </is>
+      </c>
+      <c r="M577" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="N577" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O577" t="inlineStr">
+        <is>
+          <t>Navan executed funding movement impacting Miraee market segment</t>
+        </is>
+      </c>
+      <c r="P577" t="inlineStr">
+        <is>
+          <t>Moderate competitive movement. Assess Miraee's product positioning relative to Navan.</t>
+        </is>
+      </c>
+      <c r="Q577" t="inlineStr">
+        <is>
+          <t>More news on this day Plans to reinstate a railway connection to Navan have moved into a crucial new phase, with a public consultation now underway on the emerging preferred route for a new line linking the County Meath town to Dublin via M3 Parkway. Get the latest news straight to your inbox! Publicly available information from Iarnród Éireann shows that the proposed Navan Railway would extend the existing commuter network from M3 Parkway, creating a largely double-track, electrified line designed to carry high frequency DART-style services between Navan and Dublin.</t>
+        </is>
+      </c>
+      <c r="R577" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="n">
+        <v>1176</v>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>Navan News</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/search?q=Navan+OR+TripActions+when:1d&amp;hl=en-US&amp;gl=US&amp;ceid=US:en</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>https://www.eagletribune.com/region/navan-launches-model-context-protocol-mcp-for-travel-expense-management/article_7d41db1f-f76c-5af6-92a1-5e3923399da9.html</t>
+        </is>
+      </c>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:01:39</t>
+        </is>
+      </c>
+      <c r="F578" t="inlineStr">
+        <is>
+          <t>Navan</t>
+        </is>
+      </c>
+      <c r="G578" t="inlineStr">
+        <is>
+          <t>Navan (Brand)</t>
+        </is>
+      </c>
+      <c r="H578" t="inlineStr">
+        <is>
+          <t>Navan Launches Model Context Protocol (MCP) for Travel &amp; Expense Management - Eagle-Tribune</t>
+        </is>
+      </c>
+      <c r="I578" t="inlineStr">
+        <is>
+          <t>Business Wire</t>
+        </is>
+      </c>
+      <c r="J578" t="inlineStr">
+        <is>
+          <t>Navan Launches MCP for Travel &amp; Expense
+PALO ALTO, Calif.--(BUSINESS WIRE)--Jul 2, 2026--
+Navan (NASDAQ: NAVN), the global AI-powered business travel and expense platform, today announced the launch of its Model Context Protocol (MCP), which allows customers to connect Navan to their existing AI tools and securely access their travel and expense data together through simple queries that use natural language.
+Javascript is required for you to be able to read premium content. Please enable it in your browser settings.
+Copyright Business Wire 2026.
+Home delivery and Digital Access customers of The Eagle-Tribune get deals for restaurants, hotels, attractions and other businesses, locally and across the country.
+See our e-edition for a full replica of today’s newspaper. On Tuesdays and Saturdays, see special digital-only news — along with entertainment, TV listings, comics and puzzles — in a newspaper-style format.
+Sorry, there are no recent results for popular commented articles.</t>
+        </is>
+      </c>
+      <c r="K578" t="inlineStr">
+        <is>
+          <t>2026-07-02 16:03:40</t>
+        </is>
+      </c>
+      <c r="L578" t="inlineStr">
+        <is>
+          <t>Product Launch</t>
+        </is>
+      </c>
+      <c r="M578" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="N578" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O578" t="inlineStr">
+        <is>
+          <t>Navan executed product launch movement impacting Miraee market segment</t>
+        </is>
+      </c>
+      <c r="P578" t="inlineStr">
+        <is>
+          <t>Standard market activity by Navan. No direct action required for Miraee.</t>
+        </is>
+      </c>
+      <c r="Q578" t="inlineStr">
+        <is>
+          <t>Navan Launches MCP for Travel &amp; Expense PALO ALTO, Calif. --(BUSINESS WIRE)--Jul 2, 2026-- Navan (NASDAQ: NAVN), the global AI-powered business travel and expense platform, today announced the launch of its Model Context Protocol (MCP), which allows customers to connect Navan to their existing AI tools and securely access their travel and expense data together through simple queries that use natural language.</t>
+        </is>
+      </c>
+      <c r="R578" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="n">
+        <v>1177</v>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>Navan News</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/search?q=Navan+OR+TripActions+when:1d&amp;hl=en-US&amp;gl=US&amp;ceid=US:en</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>https://www.meathchronicle.ie/2026/07/02/wood-you-believe-it-jims-stickmen-log-a-lasting-impression-on-navan-school/</t>
+        </is>
+      </c>
+      <c r="E579" t="inlineStr">
+        <is>
+          <t>2026-07-02 10:05:37</t>
+        </is>
+      </c>
+      <c r="F579" t="inlineStr">
+        <is>
+          <t>Navan</t>
+        </is>
+      </c>
+      <c r="G579" t="inlineStr">
+        <is>
+          <t>Navan (Brand)</t>
+        </is>
+      </c>
+      <c r="H579" t="inlineStr">
+        <is>
+          <t>Wood you believe it… Jim’s Stickmen log a lasting impression on Navan school - Meath Chronicle</t>
+        </is>
+      </c>
+      <c r="I579" t="inlineStr">
+        <is>
+          <t>Published:
+Thu 2 Jul 2026, 11:05 AM</t>
+        </is>
+      </c>
+      <c r="J579" t="inlineStr">
+        <is>
+          <t>When Jim McKenna first began making quirky wooden stickmen in his shed almost a decade ago, he never imagined they would inspire communities across Ireland or leave a lasting mark on a school in Navan.
+Known affectionately as the ‘The Stickman’, the Kilnaleck native has donated thousands of his handcrafted creations to charity raffles, helping schools, clubs, community groups and families in need. Earlier this year, one of those raffles helped St Oliver Plunkett NS raise funds for new sensory equipment.
+But Jim's generosity didn't stop there.
+Rather than asking for a donation to one of the many charities he regularly supports, Jim requested that the proceeds remain with the school and be used to purchase sensory resources for its pupils. The money helped provide a number of tongue drums, adding another valuable resource to the school's sensory provision.
+Determined to do even more, Jim later returned to transform part of the school's sensory garden with a collection of handcrafted wooden creations. Among them is the striking Starfish Thrower, inspired by the well-known story of the little boy who returns stranded starfish to the sea, despite being told he could never save them all. His simple reply – ‘I made a difference to that one’ – has become a powerful reminder that even the smallest act of kindness can change a life.
+The garden also features a handcrafted bird feeder café, an Antarctic penguin water station and a range of imaginative wooden installations designed to encourage outdoor learning.
+Jim hopes the sensory garden will do more than simply brighten the school grounds. He hopes it will inspire the next generation to use their own talents, whatever they may be, to help others and make a positive difference in their communities.
+For the children of St Oliver Plunkett NS, the garden is a much-loved outdoor space. For the school community, it stands as a lasting example of the difference one person's generosity can make.
+As Jim has always said, the focus should never be on the stickmen themselves, but on the people and causes they are helping. His latest gift to St Oliver Plunkett NS is another quiet reminder that kindness, when shared, has a remarkable way of growing.
+Photos of Jim McKenna installing the stickmen in St Oliver's.</t>
+        </is>
+      </c>
+      <c r="K579" t="inlineStr">
+        <is>
+          <t>2026-07-02 16:03:40</t>
+        </is>
+      </c>
+      <c r="L579" t="inlineStr">
+        <is>
+          <t>Funding</t>
+        </is>
+      </c>
+      <c r="M579" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="N579" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O579" t="inlineStr">
+        <is>
+          <t>Navan executed funding movement impacting Miraee market segment</t>
+        </is>
+      </c>
+      <c r="P579" t="inlineStr">
+        <is>
+          <t>Moderate competitive movement. Assess Miraee's product positioning relative to Navan.</t>
+        </is>
+      </c>
+      <c r="Q579" t="inlineStr">
+        <is>
+          <t>When Jim McKenna first began making quirky wooden stickmen in his shed almost a decade ago, he never imagined they would inspire communities across Ireland or leave a lasting mark on a school in Navan. Known affectionately as the ‘The Stickman’, the Kilnaleck native has donated thousands of his handcrafted creations to charity raffles, helping schools, clubs, community groups and families in need.</t>
+        </is>
+      </c>
+      <c r="R579" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="n">
+        <v>1178</v>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>Navan News</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/search?q=Navan+OR+TripActions+when:1d&amp;hl=en-US&amp;gl=US&amp;ceid=US:en</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>https://www.joplinglobe.com/region/national_business/navan-launches-model-context-protocol-mcp-for-travel-expense-management/article_708971cb-448c-5edb-bb5e-01503097bc4d.html</t>
+        </is>
+      </c>
+      <c r="E580" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:01:39</t>
+        </is>
+      </c>
+      <c r="F580" t="inlineStr">
+        <is>
+          <t>Navan</t>
+        </is>
+      </c>
+      <c r="G580" t="inlineStr">
+        <is>
+          <t>Navan (Brand)</t>
+        </is>
+      </c>
+      <c r="H580" t="inlineStr">
+        <is>
+          <t>Navan Launches Model Context Protocol (MCP) for Travel &amp; Expense Management - The Joplin Globe</t>
+        </is>
+      </c>
+      <c r="I580" t="inlineStr">
+        <is>
+          <t>Business Wire</t>
+        </is>
+      </c>
+      <c r="J580" t="inlineStr">
+        <is>
+          <t>Navan Launches MCP for Travel &amp; Expense
+PALO ALTO, Calif.--(BUSINESS WIRE)--Jul 2, 2026--
+Navan (NASDAQ: NAVN), the global AI-powered business travel and expense platform, today announced the launch of its Model Context Protocol (MCP), which allows customers to connect Navan to their existing AI tools and securely access their travel and expense data together through simple queries that use natural language.
+Javascript is required for you to be able to read premium content. Please enable it in your browser settings.
+Copyright Business Wire 2026.
+Sorry, there are no recent results for popular videos.
+Sorry, there are no recent results for popular commented articles.</t>
+        </is>
+      </c>
+      <c r="K580" t="inlineStr">
+        <is>
+          <t>2026-07-02 16:03:40</t>
+        </is>
+      </c>
+      <c r="L580" t="inlineStr">
+        <is>
+          <t>Product Launch</t>
+        </is>
+      </c>
+      <c r="M580" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="N580" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O580" t="inlineStr">
+        <is>
+          <t>Navan executed product launch movement impacting Miraee market segment</t>
+        </is>
+      </c>
+      <c r="P580" t="inlineStr">
+        <is>
+          <t>Standard market activity by Navan. No direct action required for Miraee.</t>
+        </is>
+      </c>
+      <c r="Q580" t="inlineStr">
+        <is>
+          <t>Navan Launches MCP for Travel &amp; Expense PALO ALTO, Calif. --(BUSINESS WIRE)--Jul 2, 2026-- Navan (NASDAQ: NAVN), the global AI-powered business travel and expense platform, today announced the launch of its Model Context Protocol (MCP), which allows customers to connect Navan to their existing AI tools and securely access their travel and expense data together through simple queries that use natural language.</t>
+        </is>
+      </c>
+      <c r="R580" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="n">
+        <v>1179</v>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>Navan News</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/search?q=Navan+OR+TripActions+when:1d&amp;hl=en-US&amp;gl=US&amp;ceid=US:en</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>https://www.bhpioneer.com/national_news/ca-navan/image_64cc554d-7ae2-5d8c-985a-eaa9c99ac8e5.html</t>
+        </is>
+      </c>
+      <c r="E581" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:01:39</t>
+        </is>
+      </c>
+      <c r="F581" t="inlineStr">
+        <is>
+          <t>Navan</t>
+        </is>
+      </c>
+      <c r="G581" t="inlineStr">
+        <is>
+          <t>Navan (Brand)</t>
+        </is>
+      </c>
+      <c r="H581" t="inlineStr">
+        <is>
+          <t>CA-NAVAN - Black Hills Pioneer</t>
+        </is>
+      </c>
+      <c r="I581" t="inlineStr">
+        <is>
+          <t>Business Wire</t>
+        </is>
+      </c>
+      <c r="J581" t="inlineStr">
+        <is>
+          <t>Navan Launches MCP for Travel &amp; Expense
+Keep it Clean. Please avoid obscene, vulgar, lewd,
+racist or sexually-oriented language.
+PLEASE TURN OFF YOUR CAPS LOCK.
+Don't Threaten. Threats of harming another
+person will not be tolerated.
+Be Truthful. Don't knowingly lie about anyone
+or anything.
+Be Nice. No racism, sexism or any sort of -ism
+that is degrading to another person.
+Be Proactive. Use the 'Report' link on
+each comment to let us know of abusive posts.
+Share with Us. We'd love to hear eyewitness
+accounts, the history behind an article.</t>
+        </is>
+      </c>
+      <c r="K581" t="inlineStr">
+        <is>
+          <t>2026-07-02 16:03:40</t>
+        </is>
+      </c>
+      <c r="L581" t="inlineStr">
+        <is>
+          <t>Product Launch</t>
+        </is>
+      </c>
+      <c r="M581" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="N581" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O581" t="inlineStr">
+        <is>
+          <t>Navan executed product launch movement impacting Miraee market segment</t>
+        </is>
+      </c>
+      <c r="P581" t="inlineStr">
+        <is>
+          <t>High competitive activity. Monitor Navan's product launch closely and evaluate defense strategies for Miraee.</t>
+        </is>
+      </c>
+      <c r="Q581" t="inlineStr">
+        <is>
+          <t>Navan Launches MCP for Travel &amp; Expense Keep it Clean. Please avoid obscene, vulgar, lewd, racist or sexually-oriented language.</t>
+        </is>
+      </c>
+      <c r="R581" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="n">
+        <v>1180</v>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>Google News Search - Ramp (Eric Glyman)</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/search?q=%22Eric%20Glyman%22%20after%3A2026-07-01&amp;hl=en-US&amp;gl=US&amp;ceid=US:en</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>https://tradersunion.com/news/market-voices/show/2549328-finetune-transfer-ups-ai/</t>
+        </is>
+      </c>
+      <c r="E582" t="inlineStr">
+        <is>
+          <t>2026-07-01 19:08:21</t>
+        </is>
+      </c>
+      <c r="F582" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="G582" t="inlineStr">
+        <is>
+          <t>Eric Glyman (Executive)</t>
+        </is>
+      </c>
+      <c r="H582" t="inlineStr">
+        <is>
+          <t>Eric Glyman: Finetune transfer method reduces model update costs - Traders Union</t>
+        </is>
+      </c>
+      <c r="I582" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J582" t="inlineStr">
+        <is>
+          <t>Advancements in model finetuning are transforming artificial intelligence economics.
+Eric Glyman announced a breakthrough that enables finetuned settings to transfer efficiently between open source AI models. Traditionally, frequent updates to these models created challenges, as any investment in finetuning could quickly become obsolete when new and improved models arrived. According to Glyman, the new approach radically lowers the cost of advancing from one model to the next by allowing previously created finetunes to be reused across model generations. This development is expected to improve resource allocation and streamline AI deployment for organizations seeking to keep up with rapid innovation cycles.
+But we saved everything 🙂.
+Glyman previously assessed the impact of increasing AI token spending by technology firms. Earlier this year, he said customer demand had driven his company’s expansion into accounting, AI, and European markets, moving beyond its original roadmap in response to client needs. These developments align with heightened industry focus on efficiency and innovation.</t>
+        </is>
+      </c>
+      <c r="K582" t="inlineStr">
+        <is>
+          <t>2026-07-02 16:03:44</t>
+        </is>
+      </c>
+      <c r="L582" t="inlineStr">
+        <is>
+          <t>Funding</t>
+        </is>
+      </c>
+      <c r="M582" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="N582" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O582" t="inlineStr">
+        <is>
+          <t>Ramp executed funding movement impacting Miraee market segment</t>
+        </is>
+      </c>
+      <c r="P582" t="inlineStr">
+        <is>
+          <t>Moderate competitive movement. Assess Miraee's product positioning relative to Ramp.</t>
+        </is>
+      </c>
+      <c r="Q582" t="inlineStr">
+        <is>
+          <t>Advancements in model finetuning are transforming artificial intelligence economics. Eric Glyman announced a breakthrough that enables finetuned settings to transfer efficiently between open source AI models.</t>
+        </is>
+      </c>
+      <c r="R582" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="n">
+        <v>1181</v>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>Google News Search - Ramp (Karim Atiyeh)</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/search?q=%22Karim%20Atiyeh%22%20after%3A2026-07-01&amp;hl=en-US&amp;gl=US&amp;ceid=US:en</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>https://tradersunion.com/news/market-voices/show/2549106-portal-task-transfer-ai/</t>
+        </is>
+      </c>
+      <c r="E583" t="inlineStr">
+        <is>
+          <t>2026-07-01 18:25:27</t>
+        </is>
+      </c>
+      <c r="F583" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="G583" t="inlineStr">
+        <is>
+          <t>Karim Atiyeh (Executive)</t>
+        </is>
+      </c>
+      <c r="H583" t="inlineStr">
+        <is>
+          <t>Karim Atiyeh: PorTAL enables task transfer without retraining model weights - Traders Union</t>
+        </is>
+      </c>
+      <c r="I583" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J583" t="inlineStr">
+        <is>
+          <t>Karim Atiyeh announced an innovation in artificial intelligence with PorTAL, a framework that separates task representation from a model's weights. Traditionally, fine-tuning requires training within a single model, making transfer between models cumbersome. PorTAL addresses this by extracting the learned task encoding, enabling users to port tasks to new models by simply fitting a thin converter, removing the need for full retraining. This approach could streamline workflows for organizations working with multiple AI systems.
+But we saved everything 🙂.
+Atiyeh recently announced a formal leadership change focused on technology and systems design at the company. Earlier, his company expanded to serve more than 70,000 businesses, emphasizing AI-driven finance at $44 billion in volume. These developments set the stage for the introduction of PorTAL.</t>
+        </is>
+      </c>
+      <c r="K583" t="inlineStr">
+        <is>
+          <t>2026-07-02 16:03:44</t>
+        </is>
+      </c>
+      <c r="L583" t="inlineStr">
+        <is>
+          <t>General Travel News</t>
+        </is>
+      </c>
+      <c r="M583" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="N583" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O583" t="inlineStr">
+        <is>
+          <t>Ramp executed general travel news movement impacting Miraee market segment</t>
+        </is>
+      </c>
+      <c r="P583" t="inlineStr">
+        <is>
+          <t>Standard market activity by Ramp. No direct action required for Miraee.</t>
+        </is>
+      </c>
+      <c r="Q583" t="inlineStr">
+        <is>
+          <t>Karim Atiyeh announced an innovation in artificial intelligence with PorTAL, a framework that separates task representation from a model's weights. Traditionally, fine-tuning requires training within a single model, making transfer between models cumbersome.</t>
+        </is>
+      </c>
+      <c r="R583" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
